--- a/resources/report/60/95/ex_imp/TID_122_VAT INVOICE_MULTI_IMP.xlsx
+++ b/resources/report/60/95/ex_imp/TID_122_VAT INVOICE_MULTI_IMP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lvthe\OneDrive\Máy tính\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\einvoicevn\resources\report\60\95\ex_imp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3E62C30-015B-45BF-8C6A-E6796D4E2D64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3430A37D-7E18-416C-A6B4-4E4E344B1458}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="754" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="754" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Invoice" sheetId="25" r:id="rId1"/>
@@ -838,7 +838,7 @@
     </font>
     <font>
       <i/>
-      <sz val="13"/>
+      <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -1331,6 +1331,165 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1358,175 +1517,16 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1810,32 +1810,32 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T47"/>
-  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.26953125" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="1.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="5.28515625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="3.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="2.7109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="1.7109375" style="1" customWidth="1"/>
-    <col min="7" max="8" width="2.7109375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="8.7109375" style="1" customWidth="1"/>
-    <col min="10" max="10" width="6.7109375" style="1" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="5.7109375" style="1" customWidth="1"/>
-    <col min="14" max="14" width="10.7109375" style="1" customWidth="1"/>
-    <col min="15" max="15" width="6.7109375" style="1" customWidth="1"/>
-    <col min="16" max="16" width="9.7109375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="2.7109375" style="1" customWidth="1"/>
-    <col min="18" max="18" width="5.7109375" style="1" customWidth="1"/>
-    <col min="19" max="19" width="7.7109375" style="1" customWidth="1"/>
-    <col min="20" max="20" width="1.7109375" style="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.28515625" style="1"/>
+    <col min="1" max="1" width="1.7265625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="5.26953125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="11.26953125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="3.7265625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="2.7265625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="1.7265625" style="1" customWidth="1"/>
+    <col min="7" max="8" width="2.7265625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="8.7265625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="6.7265625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="7.7265625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="4.7265625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="5.7265625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="10.7265625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="6.7265625" style="1" customWidth="1"/>
+    <col min="16" max="16" width="9.7265625" style="1" customWidth="1"/>
+    <col min="17" max="17" width="2.7265625" style="1" customWidth="1"/>
+    <col min="18" max="18" width="5.7265625" style="1" customWidth="1"/>
+    <col min="19" max="19" width="7.7265625" style="1" customWidth="1"/>
+    <col min="20" max="20" width="1.7265625" style="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.26953125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="4.9000000000000004" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:20" s="7" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" ht="4.9000000000000004" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="2" spans="1:20" s="7" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="21"/>
       <c r="B2" s="22"/>
       <c r="C2" s="22"/>
@@ -1843,25 +1843,25 @@
       <c r="E2" s="22"/>
       <c r="F2" s="22"/>
       <c r="G2" s="22"/>
-      <c r="H2" s="83" t="s">
+      <c r="H2" s="136" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="83"/>
-      <c r="J2" s="83"/>
-      <c r="K2" s="83"/>
-      <c r="L2" s="83"/>
-      <c r="M2" s="83"/>
-      <c r="N2" s="83"/>
-      <c r="O2" s="88" t="s">
+      <c r="I2" s="136"/>
+      <c r="J2" s="136"/>
+      <c r="K2" s="136"/>
+      <c r="L2" s="136"/>
+      <c r="M2" s="136"/>
+      <c r="N2" s="136"/>
+      <c r="O2" s="140" t="s">
         <v>45</v>
       </c>
-      <c r="P2" s="88"/>
-      <c r="Q2" s="78"/>
-      <c r="R2" s="78"/>
-      <c r="S2" s="78"/>
+      <c r="P2" s="140"/>
+      <c r="Q2" s="131"/>
+      <c r="R2" s="131"/>
+      <c r="S2" s="131"/>
       <c r="T2" s="23"/>
     </row>
-    <row r="3" spans="1:20" s="7" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" s="7" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="24"/>
       <c r="B3" s="9"/>
       <c r="C3" s="9"/>
@@ -1869,13 +1869,13 @@
       <c r="E3" s="9"/>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
-      <c r="H3" s="84"/>
-      <c r="I3" s="84"/>
-      <c r="J3" s="84"/>
-      <c r="K3" s="84"/>
-      <c r="L3" s="84"/>
-      <c r="M3" s="84"/>
-      <c r="N3" s="84"/>
+      <c r="H3" s="137"/>
+      <c r="I3" s="137"/>
+      <c r="J3" s="137"/>
+      <c r="K3" s="137"/>
+      <c r="L3" s="137"/>
+      <c r="M3" s="137"/>
+      <c r="N3" s="137"/>
       <c r="O3" s="50"/>
       <c r="P3" s="50"/>
       <c r="Q3" s="57"/>
@@ -1883,7 +1883,7 @@
       <c r="S3" s="57"/>
       <c r="T3" s="25"/>
     </row>
-    <row r="4" spans="1:20" s="7" customFormat="1" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" s="7" customFormat="1" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="24"/>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
@@ -1891,13 +1891,13 @@
       <c r="E4" s="9"/>
       <c r="F4" s="9"/>
       <c r="G4" s="9"/>
-      <c r="H4" s="84"/>
-      <c r="I4" s="84"/>
-      <c r="J4" s="84"/>
-      <c r="K4" s="84"/>
-      <c r="L4" s="84"/>
-      <c r="M4" s="84"/>
-      <c r="N4" s="84"/>
+      <c r="H4" s="137"/>
+      <c r="I4" s="137"/>
+      <c r="J4" s="137"/>
+      <c r="K4" s="137"/>
+      <c r="L4" s="137"/>
+      <c r="M4" s="137"/>
+      <c r="N4" s="137"/>
       <c r="O4" s="18"/>
       <c r="P4" s="18"/>
       <c r="Q4" s="57"/>
@@ -1913,25 +1913,25 @@
       <c r="E5" s="9"/>
       <c r="F5" s="9"/>
       <c r="G5" s="9"/>
-      <c r="H5" s="86" t="s">
+      <c r="H5" s="139" t="s">
         <v>18</v>
       </c>
-      <c r="I5" s="86"/>
-      <c r="J5" s="86"/>
-      <c r="K5" s="86"/>
-      <c r="L5" s="86"/>
-      <c r="M5" s="86"/>
-      <c r="N5" s="86"/>
-      <c r="O5" s="85" t="s">
+      <c r="I5" s="139"/>
+      <c r="J5" s="139"/>
+      <c r="K5" s="139"/>
+      <c r="L5" s="139"/>
+      <c r="M5" s="139"/>
+      <c r="N5" s="139"/>
+      <c r="O5" s="138" t="s">
         <v>46</v>
       </c>
-      <c r="P5" s="85"/>
-      <c r="Q5" s="98"/>
-      <c r="R5" s="98"/>
-      <c r="S5" s="98"/>
+      <c r="P5" s="138"/>
+      <c r="Q5" s="123"/>
+      <c r="R5" s="123"/>
+      <c r="S5" s="123"/>
       <c r="T5" s="25"/>
     </row>
-    <row r="6" spans="1:20" s="7" customFormat="1" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" s="7" customFormat="1" ht="13.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="24"/>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
@@ -1939,13 +1939,13 @@
       <c r="E6" s="9"/>
       <c r="F6" s="9"/>
       <c r="G6" s="9"/>
-      <c r="H6" s="87"/>
-      <c r="I6" s="87"/>
-      <c r="J6" s="87"/>
-      <c r="K6" s="87"/>
-      <c r="L6" s="87"/>
-      <c r="M6" s="87"/>
-      <c r="N6" s="87"/>
+      <c r="H6" s="79"/>
+      <c r="I6" s="79"/>
+      <c r="J6" s="79"/>
+      <c r="K6" s="79"/>
+      <c r="L6" s="79"/>
+      <c r="M6" s="79"/>
+      <c r="N6" s="79"/>
       <c r="O6" s="50"/>
       <c r="P6" s="50"/>
       <c r="Q6" s="57"/>
@@ -1953,7 +1953,7 @@
       <c r="S6" s="57"/>
       <c r="T6" s="25"/>
     </row>
-    <row r="7" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:20" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="26"/>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
@@ -1961,23 +1961,23 @@
       <c r="E7" s="8"/>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
-      <c r="H7" s="99" t="s">
+      <c r="H7" s="124" t="s">
         <v>25</v>
       </c>
-      <c r="I7" s="99"/>
-      <c r="J7" s="99"/>
-      <c r="K7" s="99"/>
-      <c r="L7" s="99"/>
-      <c r="M7" s="99"/>
-      <c r="N7" s="99"/>
-      <c r="O7" s="85"/>
-      <c r="P7" s="85"/>
-      <c r="Q7" s="101"/>
-      <c r="R7" s="101"/>
-      <c r="S7" s="101"/>
+      <c r="I7" s="124"/>
+      <c r="J7" s="124"/>
+      <c r="K7" s="124"/>
+      <c r="L7" s="124"/>
+      <c r="M7" s="124"/>
+      <c r="N7" s="124"/>
+      <c r="O7" s="138"/>
+      <c r="P7" s="138"/>
+      <c r="Q7" s="126"/>
+      <c r="R7" s="126"/>
+      <c r="S7" s="126"/>
       <c r="T7" s="27"/>
     </row>
-    <row r="8" spans="1:20" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="26"/>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
@@ -1985,13 +1985,13 @@
       <c r="E8" s="8"/>
       <c r="F8" s="11"/>
       <c r="G8" s="11"/>
-      <c r="H8" s="90"/>
-      <c r="I8" s="90"/>
-      <c r="J8" s="90"/>
-      <c r="K8" s="90"/>
-      <c r="L8" s="90"/>
-      <c r="M8" s="90"/>
-      <c r="N8" s="90"/>
+      <c r="H8" s="141"/>
+      <c r="I8" s="141"/>
+      <c r="J8" s="141"/>
+      <c r="K8" s="141"/>
+      <c r="L8" s="141"/>
+      <c r="M8" s="141"/>
+      <c r="N8" s="141"/>
       <c r="O8" s="62"/>
       <c r="P8" s="62"/>
       <c r="Q8" s="62"/>
@@ -1999,7 +1999,7 @@
       <c r="S8" s="62"/>
       <c r="T8" s="27"/>
     </row>
-    <row r="9" spans="1:20" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="26"/>
       <c r="B9" s="17"/>
       <c r="C9" s="17"/>
@@ -2021,11 +2021,11 @@
       <c r="S9" s="17"/>
       <c r="T9" s="28"/>
     </row>
-    <row r="10" spans="1:20" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="26"/>
       <c r="T10" s="28"/>
     </row>
-    <row r="11" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="26"/>
       <c r="B11" s="2" t="s">
         <v>40</v>
@@ -2036,22 +2036,22 @@
       <c r="F11" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G11" s="102"/>
-      <c r="H11" s="102"/>
-      <c r="I11" s="102"/>
-      <c r="J11" s="102"/>
-      <c r="K11" s="102"/>
-      <c r="L11" s="102"/>
-      <c r="M11" s="102"/>
-      <c r="N11" s="102"/>
-      <c r="O11" s="102"/>
-      <c r="P11" s="102"/>
-      <c r="Q11" s="102"/>
-      <c r="R11" s="102"/>
-      <c r="S11" s="102"/>
+      <c r="G11" s="127"/>
+      <c r="H11" s="127"/>
+      <c r="I11" s="127"/>
+      <c r="J11" s="127"/>
+      <c r="K11" s="127"/>
+      <c r="L11" s="127"/>
+      <c r="M11" s="127"/>
+      <c r="N11" s="127"/>
+      <c r="O11" s="127"/>
+      <c r="P11" s="127"/>
+      <c r="Q11" s="127"/>
+      <c r="R11" s="127"/>
+      <c r="S11" s="127"/>
       <c r="T11" s="28"/>
     </row>
-    <row r="12" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="26"/>
       <c r="B12" s="2" t="s">
         <v>41</v>
@@ -2062,22 +2062,22 @@
       <c r="F12" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G12" s="103"/>
-      <c r="H12" s="103"/>
-      <c r="I12" s="103"/>
-      <c r="J12" s="103"/>
-      <c r="K12" s="103"/>
-      <c r="L12" s="103"/>
-      <c r="M12" s="103"/>
-      <c r="N12" s="103"/>
-      <c r="O12" s="103"/>
-      <c r="P12" s="103"/>
-      <c r="Q12" s="103"/>
-      <c r="R12" s="103"/>
-      <c r="S12" s="103"/>
+      <c r="G12" s="128"/>
+      <c r="H12" s="128"/>
+      <c r="I12" s="128"/>
+      <c r="J12" s="128"/>
+      <c r="K12" s="128"/>
+      <c r="L12" s="128"/>
+      <c r="M12" s="128"/>
+      <c r="N12" s="128"/>
+      <c r="O12" s="128"/>
+      <c r="P12" s="128"/>
+      <c r="Q12" s="128"/>
+      <c r="R12" s="128"/>
+      <c r="S12" s="128"/>
       <c r="T12" s="28"/>
     </row>
-    <row r="13" spans="1:20" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="26"/>
       <c r="B13" s="2" t="s">
         <v>42</v>
@@ -2088,22 +2088,22 @@
       <c r="F13" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G13" s="104"/>
-      <c r="H13" s="104"/>
-      <c r="I13" s="104"/>
-      <c r="J13" s="104"/>
-      <c r="K13" s="104"/>
-      <c r="L13" s="104"/>
-      <c r="M13" s="104"/>
-      <c r="N13" s="104"/>
-      <c r="O13" s="104"/>
-      <c r="P13" s="104"/>
-      <c r="Q13" s="104"/>
-      <c r="R13" s="104"/>
-      <c r="S13" s="104"/>
+      <c r="G13" s="129"/>
+      <c r="H13" s="129"/>
+      <c r="I13" s="129"/>
+      <c r="J13" s="129"/>
+      <c r="K13" s="129"/>
+      <c r="L13" s="129"/>
+      <c r="M13" s="129"/>
+      <c r="N13" s="129"/>
+      <c r="O13" s="129"/>
+      <c r="P13" s="129"/>
+      <c r="Q13" s="129"/>
+      <c r="R13" s="129"/>
+      <c r="S13" s="129"/>
       <c r="T13" s="28"/>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A14" s="26"/>
       <c r="B14" s="71" t="s">
         <v>43</v>
@@ -2112,10 +2112,10 @@
       <c r="F14" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G14" s="89"/>
-      <c r="H14" s="89"/>
-      <c r="I14" s="89"/>
-      <c r="J14" s="89"/>
+      <c r="G14" s="130"/>
+      <c r="H14" s="130"/>
+      <c r="I14" s="130"/>
+      <c r="J14" s="130"/>
       <c r="K14" s="16"/>
       <c r="L14" s="16"/>
       <c r="M14" s="16"/>
@@ -2127,7 +2127,7 @@
       <c r="S14" s="15"/>
       <c r="T14" s="28"/>
     </row>
-    <row r="15" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="26"/>
       <c r="B15" s="71" t="s">
         <v>44</v>
@@ -2136,22 +2136,22 @@
       <c r="F15" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G15" s="89"/>
-      <c r="H15" s="89"/>
-      <c r="I15" s="89"/>
-      <c r="J15" s="89"/>
-      <c r="K15" s="91"/>
-      <c r="L15" s="91"/>
-      <c r="M15" s="91"/>
-      <c r="N15" s="91"/>
-      <c r="O15" s="91"/>
-      <c r="P15" s="91"/>
-      <c r="Q15" s="91"/>
-      <c r="R15" s="91"/>
-      <c r="S15" s="91"/>
+      <c r="G15" s="130"/>
+      <c r="H15" s="130"/>
+      <c r="I15" s="130"/>
+      <c r="J15" s="130"/>
+      <c r="K15" s="122"/>
+      <c r="L15" s="122"/>
+      <c r="M15" s="122"/>
+      <c r="N15" s="122"/>
+      <c r="O15" s="122"/>
+      <c r="P15" s="122"/>
+      <c r="Q15" s="122"/>
+      <c r="R15" s="122"/>
+      <c r="S15" s="122"/>
       <c r="T15" s="28"/>
     </row>
-    <row r="16" spans="1:20" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="26"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -2173,79 +2173,79 @@
       <c r="S16" s="3"/>
       <c r="T16" s="28"/>
     </row>
-    <row r="17" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="29"/>
       <c r="B17" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="I17" s="100"/>
-      <c r="J17" s="100"/>
-      <c r="K17" s="100"/>
-      <c r="L17" s="100"/>
-      <c r="M17" s="100"/>
-      <c r="N17" s="100"/>
-      <c r="O17" s="100"/>
-      <c r="P17" s="100"/>
-      <c r="Q17" s="100"/>
-      <c r="R17" s="100"/>
-      <c r="S17" s="100"/>
+      <c r="I17" s="125"/>
+      <c r="J17" s="125"/>
+      <c r="K17" s="125"/>
+      <c r="L17" s="125"/>
+      <c r="M17" s="125"/>
+      <c r="N17" s="125"/>
+      <c r="O17" s="125"/>
+      <c r="P17" s="125"/>
+      <c r="Q17" s="125"/>
+      <c r="R17" s="125"/>
+      <c r="S17" s="125"/>
       <c r="T17" s="30"/>
     </row>
-    <row r="18" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="29"/>
       <c r="B18" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="H18" s="89"/>
-      <c r="I18" s="89"/>
-      <c r="J18" s="89"/>
-      <c r="K18" s="89"/>
-      <c r="L18" s="89"/>
-      <c r="M18" s="89"/>
-      <c r="N18" s="89"/>
-      <c r="O18" s="89"/>
-      <c r="P18" s="89"/>
-      <c r="Q18" s="89"/>
-      <c r="R18" s="89"/>
-      <c r="S18" s="89"/>
+      <c r="H18" s="130"/>
+      <c r="I18" s="130"/>
+      <c r="J18" s="130"/>
+      <c r="K18" s="130"/>
+      <c r="L18" s="130"/>
+      <c r="M18" s="130"/>
+      <c r="N18" s="130"/>
+      <c r="O18" s="130"/>
+      <c r="P18" s="130"/>
+      <c r="Q18" s="130"/>
+      <c r="R18" s="130"/>
+      <c r="S18" s="130"/>
       <c r="T18" s="30"/>
     </row>
-    <row r="19" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="29"/>
       <c r="B19" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E19" s="89"/>
-      <c r="F19" s="89"/>
-      <c r="G19" s="89"/>
-      <c r="H19" s="89"/>
-      <c r="I19" s="89"/>
+      <c r="E19" s="130"/>
+      <c r="F19" s="130"/>
+      <c r="G19" s="130"/>
+      <c r="H19" s="130"/>
+      <c r="I19" s="130"/>
       <c r="T19" s="30"/>
     </row>
-    <row r="20" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="29"/>
       <c r="B20" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D20" s="79"/>
-      <c r="E20" s="79"/>
-      <c r="F20" s="79"/>
-      <c r="G20" s="79"/>
-      <c r="H20" s="79"/>
-      <c r="I20" s="79"/>
-      <c r="J20" s="79"/>
-      <c r="K20" s="79"/>
-      <c r="L20" s="79"/>
-      <c r="M20" s="79"/>
-      <c r="N20" s="79"/>
-      <c r="O20" s="79"/>
-      <c r="P20" s="79"/>
-      <c r="Q20" s="79"/>
-      <c r="R20" s="79"/>
-      <c r="S20" s="79"/>
+      <c r="D20" s="132"/>
+      <c r="E20" s="132"/>
+      <c r="F20" s="132"/>
+      <c r="G20" s="132"/>
+      <c r="H20" s="132"/>
+      <c r="I20" s="132"/>
+      <c r="J20" s="132"/>
+      <c r="K20" s="132"/>
+      <c r="L20" s="132"/>
+      <c r="M20" s="132"/>
+      <c r="N20" s="132"/>
+      <c r="O20" s="132"/>
+      <c r="P20" s="132"/>
+      <c r="Q20" s="132"/>
+      <c r="R20" s="132"/>
+      <c r="S20" s="132"/>
       <c r="T20" s="30"/>
     </row>
-    <row r="21" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="29"/>
       <c r="B21" s="2" t="s">
         <v>49</v>
@@ -2256,9 +2256,9 @@
       <c r="G21" s="55"/>
       <c r="H21" s="55"/>
       <c r="I21" s="55"/>
-      <c r="J21" s="79"/>
-      <c r="K21" s="79"/>
-      <c r="L21" s="79"/>
+      <c r="J21" s="132"/>
+      <c r="K21" s="132"/>
+      <c r="L21" s="132"/>
       <c r="M21" s="55"/>
       <c r="N21" s="55"/>
       <c r="O21" s="55"/>
@@ -2268,51 +2268,51 @@
       <c r="S21" s="55"/>
       <c r="T21" s="30"/>
     </row>
-    <row r="22" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="29"/>
       <c r="B22" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F22" s="89"/>
-      <c r="G22" s="89"/>
-      <c r="H22" s="89"/>
-      <c r="I22" s="89"/>
+      <c r="F22" s="130"/>
+      <c r="G22" s="130"/>
+      <c r="H22" s="130"/>
+      <c r="I22" s="130"/>
       <c r="M22" s="56" t="s">
         <v>50</v>
       </c>
-      <c r="P22" s="99"/>
-      <c r="Q22" s="99"/>
-      <c r="R22" s="99"/>
+      <c r="P22" s="124"/>
+      <c r="Q22" s="124"/>
+      <c r="R22" s="124"/>
       <c r="T22" s="30"/>
     </row>
-    <row r="23" spans="1:20" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:20" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="26"/>
       <c r="T23" s="28"/>
     </row>
-    <row r="24" spans="1:20" s="43" customFormat="1" ht="28.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:20" s="43" customFormat="1" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="39"/>
       <c r="B24" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="C24" s="80" t="s">
+      <c r="C24" s="133" t="s">
         <v>1</v>
       </c>
-      <c r="D24" s="82"/>
-      <c r="E24" s="82"/>
-      <c r="F24" s="82"/>
-      <c r="G24" s="82"/>
-      <c r="H24" s="82"/>
-      <c r="I24" s="81"/>
+      <c r="D24" s="135"/>
+      <c r="E24" s="135"/>
+      <c r="F24" s="135"/>
+      <c r="G24" s="135"/>
+      <c r="H24" s="135"/>
+      <c r="I24" s="134"/>
       <c r="J24" s="40" t="s">
         <v>3</v>
       </c>
       <c r="K24" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="L24" s="80" t="s">
+      <c r="L24" s="133" t="s">
         <v>13</v>
       </c>
-      <c r="M24" s="81"/>
+      <c r="M24" s="134"/>
       <c r="N24" s="40" t="s">
         <v>2</v>
       </c>
@@ -2322,37 +2322,37 @@
       <c r="P24" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="Q24" s="80" t="s">
+      <c r="Q24" s="133" t="s">
         <v>35</v>
       </c>
-      <c r="R24" s="82"/>
-      <c r="S24" s="81"/>
+      <c r="R24" s="135"/>
+      <c r="S24" s="134"/>
       <c r="T24" s="42"/>
     </row>
-    <row r="25" spans="1:20" s="47" customFormat="1" ht="28.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:20" s="47" customFormat="1" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="44"/>
       <c r="B25" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="92" t="s">
+      <c r="C25" s="115" t="s">
         <v>7</v>
       </c>
-      <c r="D25" s="93"/>
-      <c r="E25" s="93"/>
-      <c r="F25" s="93"/>
-      <c r="G25" s="93"/>
-      <c r="H25" s="93"/>
-      <c r="I25" s="94"/>
+      <c r="D25" s="120"/>
+      <c r="E25" s="120"/>
+      <c r="F25" s="120"/>
+      <c r="G25" s="120"/>
+      <c r="H25" s="120"/>
+      <c r="I25" s="116"/>
       <c r="J25" s="45" t="s">
         <v>8</v>
       </c>
       <c r="K25" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="L25" s="92" t="s">
+      <c r="L25" s="115" t="s">
         <v>21</v>
       </c>
-      <c r="M25" s="94"/>
+      <c r="M25" s="116"/>
       <c r="N25" s="45" t="s">
         <v>9</v>
       </c>
@@ -2362,37 +2362,37 @@
       <c r="P25" s="53" t="s">
         <v>33</v>
       </c>
-      <c r="Q25" s="92" t="s">
+      <c r="Q25" s="115" t="s">
         <v>34</v>
       </c>
-      <c r="R25" s="93"/>
-      <c r="S25" s="94"/>
+      <c r="R25" s="120"/>
+      <c r="S25" s="116"/>
       <c r="T25" s="46"/>
     </row>
-    <row r="26" spans="1:20" s="5" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A26" s="32"/>
       <c r="B26" s="4">
         <v>1</v>
       </c>
-      <c r="C26" s="95">
+      <c r="C26" s="117">
         <v>2</v>
       </c>
-      <c r="D26" s="97"/>
-      <c r="E26" s="97"/>
-      <c r="F26" s="97"/>
-      <c r="G26" s="97"/>
-      <c r="H26" s="97"/>
-      <c r="I26" s="96"/>
+      <c r="D26" s="118"/>
+      <c r="E26" s="118"/>
+      <c r="F26" s="118"/>
+      <c r="G26" s="118"/>
+      <c r="H26" s="118"/>
+      <c r="I26" s="119"/>
       <c r="J26" s="4">
         <v>3</v>
       </c>
       <c r="K26" s="4">
         <v>4</v>
       </c>
-      <c r="L26" s="95">
+      <c r="L26" s="117">
         <v>5</v>
       </c>
-      <c r="M26" s="96"/>
+      <c r="M26" s="119"/>
       <c r="N26" s="4" t="s">
         <v>19</v>
       </c>
@@ -2402,36 +2402,36 @@
       <c r="P26" s="37">
         <v>8</v>
       </c>
-      <c r="Q26" s="95" t="s">
+      <c r="Q26" s="117" t="s">
         <v>29</v>
       </c>
-      <c r="R26" s="97"/>
-      <c r="S26" s="96"/>
+      <c r="R26" s="118"/>
+      <c r="S26" s="119"/>
       <c r="T26" s="58"/>
     </row>
-    <row r="27" spans="1:20" s="11" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:20" s="11" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="33"/>
       <c r="B27" s="72"/>
-      <c r="C27" s="111"/>
-      <c r="D27" s="111"/>
-      <c r="E27" s="111"/>
-      <c r="F27" s="111"/>
-      <c r="G27" s="111"/>
-      <c r="H27" s="111"/>
-      <c r="I27" s="111"/>
+      <c r="C27" s="121"/>
+      <c r="D27" s="121"/>
+      <c r="E27" s="121"/>
+      <c r="F27" s="121"/>
+      <c r="G27" s="121"/>
+      <c r="H27" s="121"/>
+      <c r="I27" s="121"/>
       <c r="J27" s="72"/>
       <c r="K27" s="73"/>
-      <c r="L27" s="108"/>
-      <c r="M27" s="110"/>
+      <c r="L27" s="112"/>
+      <c r="M27" s="114"/>
       <c r="N27" s="73"/>
       <c r="O27" s="74"/>
       <c r="P27" s="75"/>
-      <c r="Q27" s="108"/>
-      <c r="R27" s="109"/>
-      <c r="S27" s="110"/>
+      <c r="Q27" s="112"/>
+      <c r="R27" s="113"/>
+      <c r="S27" s="114"/>
       <c r="T27" s="59"/>
     </row>
-    <row r="28" spans="1:20" s="50" customFormat="1" ht="25.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:20" s="50" customFormat="1" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="48"/>
       <c r="B28" s="49"/>
       <c r="C28" s="65"/>
@@ -2441,25 +2441,25 @@
       <c r="G28" s="65"/>
       <c r="H28" s="65"/>
       <c r="I28" s="66"/>
-      <c r="J28" s="105" t="s">
+      <c r="J28" s="109" t="s">
         <v>37</v>
       </c>
-      <c r="K28" s="106"/>
-      <c r="L28" s="106"/>
-      <c r="M28" s="107"/>
-      <c r="N28" s="105" t="s">
+      <c r="K28" s="110"/>
+      <c r="L28" s="110"/>
+      <c r="M28" s="111"/>
+      <c r="N28" s="109" t="s">
         <v>28</v>
       </c>
-      <c r="O28" s="106"/>
-      <c r="P28" s="107"/>
-      <c r="Q28" s="105" t="s">
+      <c r="O28" s="110"/>
+      <c r="P28" s="111"/>
+      <c r="Q28" s="109" t="s">
         <v>47</v>
       </c>
-      <c r="R28" s="106"/>
-      <c r="S28" s="107"/>
+      <c r="R28" s="110"/>
+      <c r="S28" s="111"/>
       <c r="T28" s="60"/>
     </row>
-    <row r="29" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="29"/>
       <c r="B29" s="51" t="s">
         <v>56</v>
@@ -2471,19 +2471,19 @@
       <c r="G29" s="12"/>
       <c r="H29" s="12"/>
       <c r="I29" s="12"/>
-      <c r="J29" s="115"/>
-      <c r="K29" s="116"/>
-      <c r="L29" s="116"/>
-      <c r="M29" s="117"/>
-      <c r="N29" s="112"/>
-      <c r="O29" s="113"/>
-      <c r="P29" s="114"/>
-      <c r="Q29" s="112"/>
-      <c r="R29" s="113"/>
-      <c r="S29" s="114"/>
+      <c r="J29" s="94"/>
+      <c r="K29" s="95"/>
+      <c r="L29" s="95"/>
+      <c r="M29" s="96"/>
+      <c r="N29" s="97"/>
+      <c r="O29" s="98"/>
+      <c r="P29" s="99"/>
+      <c r="Q29" s="97"/>
+      <c r="R29" s="98"/>
+      <c r="S29" s="99"/>
       <c r="T29" s="67"/>
     </row>
-    <row r="30" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="29"/>
       <c r="B30" s="51" t="s">
         <v>59</v>
@@ -2495,19 +2495,19 @@
       <c r="G30" s="12"/>
       <c r="H30" s="12"/>
       <c r="I30" s="12"/>
-      <c r="J30" s="115"/>
-      <c r="K30" s="116"/>
-      <c r="L30" s="116"/>
-      <c r="M30" s="117"/>
-      <c r="N30" s="112"/>
-      <c r="O30" s="113"/>
-      <c r="P30" s="114"/>
-      <c r="Q30" s="112"/>
-      <c r="R30" s="113"/>
-      <c r="S30" s="114"/>
+      <c r="J30" s="94"/>
+      <c r="K30" s="95"/>
+      <c r="L30" s="95"/>
+      <c r="M30" s="96"/>
+      <c r="N30" s="97"/>
+      <c r="O30" s="98"/>
+      <c r="P30" s="99"/>
+      <c r="Q30" s="97"/>
+      <c r="R30" s="98"/>
+      <c r="S30" s="99"/>
       <c r="T30" s="67"/>
     </row>
-    <row r="31" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="29"/>
       <c r="B31" s="51" t="s">
         <v>53</v>
@@ -2519,19 +2519,19 @@
       <c r="G31" s="12"/>
       <c r="H31" s="12"/>
       <c r="I31" s="12"/>
-      <c r="J31" s="115"/>
-      <c r="K31" s="116"/>
-      <c r="L31" s="116"/>
-      <c r="M31" s="117"/>
-      <c r="N31" s="112"/>
-      <c r="O31" s="113"/>
-      <c r="P31" s="114"/>
-      <c r="Q31" s="112"/>
-      <c r="R31" s="113"/>
-      <c r="S31" s="114"/>
+      <c r="J31" s="94"/>
+      <c r="K31" s="95"/>
+      <c r="L31" s="95"/>
+      <c r="M31" s="96"/>
+      <c r="N31" s="97"/>
+      <c r="O31" s="98"/>
+      <c r="P31" s="99"/>
+      <c r="Q31" s="97"/>
+      <c r="R31" s="98"/>
+      <c r="S31" s="99"/>
       <c r="T31" s="67"/>
     </row>
-    <row r="32" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="29"/>
       <c r="B32" s="51" t="s">
         <v>54</v>
@@ -2543,19 +2543,19 @@
       <c r="G32" s="12"/>
       <c r="H32" s="12"/>
       <c r="I32" s="12"/>
-      <c r="J32" s="115"/>
-      <c r="K32" s="116"/>
-      <c r="L32" s="116"/>
-      <c r="M32" s="117"/>
-      <c r="N32" s="112"/>
-      <c r="O32" s="113"/>
-      <c r="P32" s="114"/>
-      <c r="Q32" s="112"/>
-      <c r="R32" s="113"/>
-      <c r="S32" s="114"/>
+      <c r="J32" s="94"/>
+      <c r="K32" s="95"/>
+      <c r="L32" s="95"/>
+      <c r="M32" s="96"/>
+      <c r="N32" s="97"/>
+      <c r="O32" s="98"/>
+      <c r="P32" s="99"/>
+      <c r="Q32" s="97"/>
+      <c r="R32" s="98"/>
+      <c r="S32" s="99"/>
       <c r="T32" s="67"/>
     </row>
-    <row r="33" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="29"/>
       <c r="B33" s="51" t="s">
         <v>55</v>
@@ -2567,19 +2567,19 @@
       <c r="G33" s="12"/>
       <c r="H33" s="12"/>
       <c r="I33" s="12"/>
-      <c r="J33" s="115"/>
-      <c r="K33" s="116"/>
-      <c r="L33" s="116"/>
-      <c r="M33" s="117"/>
-      <c r="N33" s="112"/>
-      <c r="O33" s="113"/>
-      <c r="P33" s="114"/>
-      <c r="Q33" s="112"/>
-      <c r="R33" s="113"/>
-      <c r="S33" s="114"/>
+      <c r="J33" s="94"/>
+      <c r="K33" s="95"/>
+      <c r="L33" s="95"/>
+      <c r="M33" s="96"/>
+      <c r="N33" s="97"/>
+      <c r="O33" s="98"/>
+      <c r="P33" s="99"/>
+      <c r="Q33" s="97"/>
+      <c r="R33" s="98"/>
+      <c r="S33" s="99"/>
       <c r="T33" s="67"/>
     </row>
-    <row r="34" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="29"/>
       <c r="B34" s="51" t="s">
         <v>52</v>
@@ -2591,19 +2591,19 @@
       <c r="G34" s="12"/>
       <c r="H34" s="12"/>
       <c r="I34" s="12"/>
-      <c r="J34" s="115"/>
-      <c r="K34" s="116"/>
-      <c r="L34" s="116"/>
-      <c r="M34" s="117"/>
-      <c r="N34" s="112"/>
-      <c r="O34" s="113"/>
-      <c r="P34" s="114"/>
-      <c r="Q34" s="112"/>
-      <c r="R34" s="113"/>
-      <c r="S34" s="114"/>
+      <c r="J34" s="94"/>
+      <c r="K34" s="95"/>
+      <c r="L34" s="95"/>
+      <c r="M34" s="96"/>
+      <c r="N34" s="97"/>
+      <c r="O34" s="98"/>
+      <c r="P34" s="99"/>
+      <c r="Q34" s="97"/>
+      <c r="R34" s="98"/>
+      <c r="S34" s="99"/>
       <c r="T34" s="67"/>
     </row>
-    <row r="35" spans="1:20" s="2" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:20" s="2" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="29"/>
       <c r="B35" s="52" t="s">
         <v>27</v>
@@ -2615,19 +2615,19 @@
       <c r="G35" s="12"/>
       <c r="H35" s="12"/>
       <c r="I35" s="12"/>
-      <c r="J35" s="120"/>
-      <c r="K35" s="121"/>
-      <c r="L35" s="121"/>
-      <c r="M35" s="122"/>
-      <c r="N35" s="120"/>
-      <c r="O35" s="121"/>
-      <c r="P35" s="122"/>
-      <c r="Q35" s="123"/>
-      <c r="R35" s="124"/>
-      <c r="S35" s="125"/>
+      <c r="J35" s="100"/>
+      <c r="K35" s="101"/>
+      <c r="L35" s="101"/>
+      <c r="M35" s="102"/>
+      <c r="N35" s="100"/>
+      <c r="O35" s="101"/>
+      <c r="P35" s="102"/>
+      <c r="Q35" s="103"/>
+      <c r="R35" s="104"/>
+      <c r="S35" s="105"/>
       <c r="T35" s="67"/>
     </row>
-    <row r="36" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="29"/>
       <c r="B36" s="20" t="s">
         <v>48</v>
@@ -2638,295 +2638,230 @@
       <c r="F36" s="12"/>
       <c r="G36" s="12"/>
       <c r="H36" s="12"/>
-      <c r="I36" s="126"/>
-      <c r="J36" s="126"/>
-      <c r="K36" s="126"/>
-      <c r="L36" s="126"/>
-      <c r="M36" s="126"/>
-      <c r="N36" s="126"/>
-      <c r="O36" s="126"/>
-      <c r="P36" s="126"/>
-      <c r="Q36" s="126"/>
-      <c r="R36" s="126"/>
-      <c r="S36" s="127"/>
+      <c r="I36" s="106"/>
+      <c r="J36" s="106"/>
+      <c r="K36" s="106"/>
+      <c r="L36" s="106"/>
+      <c r="M36" s="106"/>
+      <c r="N36" s="106"/>
+      <c r="O36" s="106"/>
+      <c r="P36" s="106"/>
+      <c r="Q36" s="106"/>
+      <c r="R36" s="106"/>
+      <c r="S36" s="107"/>
       <c r="T36" s="67"/>
     </row>
-    <row r="37" spans="1:20" s="10" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:20" s="10" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="34"/>
-      <c r="B37" s="128" t="s">
+      <c r="B37" s="108" t="s">
         <v>17</v>
       </c>
-      <c r="C37" s="128"/>
-      <c r="D37" s="128"/>
-      <c r="E37" s="128"/>
-      <c r="F37" s="128"/>
-      <c r="G37" s="128"/>
-      <c r="H37" s="128"/>
-      <c r="I37" s="128"/>
-      <c r="J37" s="128"/>
-      <c r="K37" s="128"/>
-      <c r="L37" s="128"/>
-      <c r="M37" s="128" t="s">
+      <c r="C37" s="108"/>
+      <c r="D37" s="108"/>
+      <c r="E37" s="108"/>
+      <c r="F37" s="108"/>
+      <c r="G37" s="108"/>
+      <c r="H37" s="108"/>
+      <c r="I37" s="108"/>
+      <c r="J37" s="108"/>
+      <c r="K37" s="108"/>
+      <c r="L37" s="108"/>
+      <c r="M37" s="108" t="s">
         <v>14</v>
       </c>
-      <c r="N37" s="128"/>
-      <c r="O37" s="128"/>
-      <c r="P37" s="128"/>
-      <c r="Q37" s="128"/>
-      <c r="R37" s="128"/>
-      <c r="S37" s="128"/>
+      <c r="N37" s="108"/>
+      <c r="O37" s="108"/>
+      <c r="P37" s="108"/>
+      <c r="Q37" s="108"/>
+      <c r="R37" s="108"/>
+      <c r="S37" s="108"/>
       <c r="T37" s="35"/>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A38" s="26"/>
-      <c r="B38" s="118" t="s">
+      <c r="B38" s="92" t="s">
         <v>11</v>
       </c>
-      <c r="C38" s="118"/>
-      <c r="D38" s="118"/>
-      <c r="E38" s="118"/>
-      <c r="F38" s="118"/>
-      <c r="G38" s="118"/>
-      <c r="H38" s="118"/>
-      <c r="I38" s="119"/>
-      <c r="J38" s="119"/>
-      <c r="K38" s="119"/>
-      <c r="L38" s="119"/>
-      <c r="M38" s="119" t="s">
+      <c r="C38" s="92"/>
+      <c r="D38" s="92"/>
+      <c r="E38" s="92"/>
+      <c r="F38" s="92"/>
+      <c r="G38" s="92"/>
+      <c r="H38" s="92"/>
+      <c r="I38" s="93"/>
+      <c r="J38" s="93"/>
+      <c r="K38" s="93"/>
+      <c r="L38" s="93"/>
+      <c r="M38" s="93" t="s">
         <v>57</v>
       </c>
-      <c r="N38" s="119"/>
-      <c r="O38" s="119"/>
-      <c r="P38" s="119"/>
-      <c r="Q38" s="119"/>
-      <c r="R38" s="119"/>
-      <c r="S38" s="119"/>
+      <c r="N38" s="93"/>
+      <c r="O38" s="93"/>
+      <c r="P38" s="93"/>
+      <c r="Q38" s="93"/>
+      <c r="R38" s="93"/>
+      <c r="S38" s="93"/>
       <c r="T38" s="31"/>
     </row>
-    <row r="39" spans="1:20" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:20" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="26"/>
-      <c r="B39" s="87" t="s">
+      <c r="B39" s="79" t="s">
         <v>12</v>
       </c>
-      <c r="C39" s="87"/>
-      <c r="D39" s="87"/>
-      <c r="E39" s="87"/>
-      <c r="F39" s="87"/>
-      <c r="G39" s="87"/>
-      <c r="H39" s="87"/>
-      <c r="I39" s="87"/>
-      <c r="J39" s="87"/>
-      <c r="K39" s="87"/>
-      <c r="L39" s="87"/>
-      <c r="M39" s="87" t="s">
+      <c r="C39" s="79"/>
+      <c r="D39" s="79"/>
+      <c r="E39" s="79"/>
+      <c r="F39" s="79"/>
+      <c r="G39" s="79"/>
+      <c r="H39" s="79"/>
+      <c r="I39" s="79"/>
+      <c r="J39" s="79"/>
+      <c r="K39" s="79"/>
+      <c r="L39" s="79"/>
+      <c r="M39" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="N39" s="87"/>
-      <c r="O39" s="87"/>
-      <c r="P39" s="87"/>
-      <c r="Q39" s="87"/>
-      <c r="R39" s="87"/>
-      <c r="S39" s="87"/>
+      <c r="N39" s="79"/>
+      <c r="O39" s="79"/>
+      <c r="P39" s="79"/>
+      <c r="Q39" s="79"/>
+      <c r="R39" s="79"/>
+      <c r="S39" s="79"/>
       <c r="T39" s="28"/>
     </row>
-    <row r="40" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="26"/>
       <c r="T40" s="28"/>
     </row>
-    <row r="41" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="26"/>
-      <c r="M41" s="130" t="s">
+      <c r="M41" s="88" t="s">
         <v>10</v>
       </c>
-      <c r="N41" s="131"/>
-      <c r="O41" s="142"/>
-      <c r="P41" s="142"/>
-      <c r="Q41" s="142"/>
-      <c r="R41" s="142"/>
-      <c r="S41" s="143"/>
+      <c r="N41" s="89"/>
+      <c r="O41" s="90"/>
+      <c r="P41" s="90"/>
+      <c r="Q41" s="90"/>
+      <c r="R41" s="90"/>
+      <c r="S41" s="91"/>
       <c r="T41" s="63"/>
     </row>
-    <row r="42" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="26"/>
       <c r="B42" s="18"/>
-      <c r="M42" s="133" t="s">
+      <c r="M42" s="81" t="s">
         <v>58</v>
       </c>
-      <c r="N42" s="134"/>
-      <c r="O42" s="135"/>
-      <c r="P42" s="135"/>
-      <c r="Q42" s="135"/>
-      <c r="R42" s="135"/>
-      <c r="S42" s="136"/>
+      <c r="N42" s="82"/>
+      <c r="O42" s="142"/>
+      <c r="P42" s="142"/>
+      <c r="Q42" s="142"/>
+      <c r="R42" s="142"/>
+      <c r="S42" s="143"/>
       <c r="T42" s="63"/>
     </row>
-    <row r="43" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="26"/>
       <c r="B43" s="19"/>
-      <c r="D43" s="132"/>
-      <c r="E43" s="132"/>
-      <c r="F43" s="132"/>
-      <c r="G43" s="132"/>
-      <c r="H43" s="132"/>
-      <c r="I43" s="132"/>
-      <c r="J43" s="132"/>
-      <c r="K43" s="132"/>
-      <c r="M43" s="137" t="s">
+      <c r="D43" s="80"/>
+      <c r="E43" s="80"/>
+      <c r="F43" s="80"/>
+      <c r="G43" s="80"/>
+      <c r="H43" s="80"/>
+      <c r="I43" s="80"/>
+      <c r="J43" s="80"/>
+      <c r="K43" s="80"/>
+      <c r="M43" s="83" t="s">
         <v>60</v>
       </c>
-      <c r="N43" s="138"/>
-      <c r="O43" s="139"/>
-      <c r="P43" s="139"/>
-      <c r="Q43" s="139"/>
-      <c r="R43" s="139"/>
+      <c r="N43" s="84"/>
+      <c r="O43" s="85"/>
+      <c r="P43" s="85"/>
+      <c r="Q43" s="85"/>
+      <c r="R43" s="85"/>
       <c r="S43" s="64"/>
       <c r="T43" s="28"/>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A44" s="26"/>
       <c r="B44" s="61" t="s">
         <v>51</v>
       </c>
-      <c r="H44" s="141"/>
-      <c r="I44" s="141"/>
-      <c r="J44" s="141"/>
-      <c r="K44" s="141"/>
+      <c r="H44" s="87"/>
+      <c r="I44" s="87"/>
+      <c r="J44" s="87"/>
+      <c r="K44" s="87"/>
       <c r="R44" s="6"/>
       <c r="S44" s="6"/>
       <c r="T44" s="28"/>
     </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A45" s="26"/>
       <c r="B45" s="77" t="s">
         <v>61</v>
       </c>
-      <c r="I45" s="141"/>
-      <c r="J45" s="141"/>
-      <c r="K45" s="141"/>
-      <c r="L45" s="141"/>
-      <c r="M45" s="141"/>
-      <c r="N45" s="141"/>
-      <c r="O45" s="141"/>
-      <c r="P45" s="141"/>
-      <c r="Q45" s="141"/>
-      <c r="R45" s="141"/>
-      <c r="S45" s="141"/>
+      <c r="I45" s="87"/>
+      <c r="J45" s="87"/>
+      <c r="K45" s="87"/>
+      <c r="L45" s="87"/>
+      <c r="M45" s="87"/>
+      <c r="N45" s="87"/>
+      <c r="O45" s="87"/>
+      <c r="P45" s="87"/>
+      <c r="Q45" s="87"/>
+      <c r="R45" s="87"/>
+      <c r="S45" s="87"/>
       <c r="T45" s="28"/>
     </row>
-    <row r="46" spans="1:20" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:20" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A46" s="36"/>
-      <c r="B46" s="140" t="s">
+      <c r="B46" s="86" t="s">
         <v>5</v>
       </c>
-      <c r="C46" s="140"/>
-      <c r="D46" s="140"/>
-      <c r="E46" s="140"/>
-      <c r="F46" s="140"/>
-      <c r="G46" s="140"/>
-      <c r="H46" s="140"/>
-      <c r="I46" s="140"/>
-      <c r="J46" s="140"/>
-      <c r="K46" s="140"/>
-      <c r="L46" s="140"/>
-      <c r="M46" s="140"/>
-      <c r="N46" s="140"/>
-      <c r="O46" s="140"/>
-      <c r="P46" s="140"/>
-      <c r="Q46" s="140"/>
-      <c r="R46" s="140"/>
-      <c r="S46" s="140"/>
+      <c r="C46" s="86"/>
+      <c r="D46" s="86"/>
+      <c r="E46" s="86"/>
+      <c r="F46" s="86"/>
+      <c r="G46" s="86"/>
+      <c r="H46" s="86"/>
+      <c r="I46" s="86"/>
+      <c r="J46" s="86"/>
+      <c r="K46" s="86"/>
+      <c r="L46" s="86"/>
+      <c r="M46" s="86"/>
+      <c r="N46" s="86"/>
+      <c r="O46" s="86"/>
+      <c r="P46" s="86"/>
+      <c r="Q46" s="86"/>
+      <c r="R46" s="86"/>
+      <c r="S46" s="86"/>
       <c r="T46" s="76"/>
     </row>
-    <row r="47" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="129" t="s">
+    <row r="47" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B47" s="78" t="s">
         <v>36</v>
       </c>
-      <c r="C47" s="129"/>
-      <c r="D47" s="129"/>
-      <c r="E47" s="129"/>
-      <c r="F47" s="129"/>
-      <c r="G47" s="129"/>
-      <c r="H47" s="129"/>
-      <c r="I47" s="129"/>
-      <c r="J47" s="129"/>
-      <c r="K47" s="129"/>
-      <c r="L47" s="129"/>
-      <c r="M47" s="129"/>
-      <c r="N47" s="129"/>
-      <c r="O47" s="129"/>
-      <c r="P47" s="129"/>
-      <c r="Q47" s="129"/>
-      <c r="R47" s="129"/>
-      <c r="S47" s="129"/>
-      <c r="T47" s="129"/>
+      <c r="C47" s="78"/>
+      <c r="D47" s="78"/>
+      <c r="E47" s="78"/>
+      <c r="F47" s="78"/>
+      <c r="G47" s="78"/>
+      <c r="H47" s="78"/>
+      <c r="I47" s="78"/>
+      <c r="J47" s="78"/>
+      <c r="K47" s="78"/>
+      <c r="L47" s="78"/>
+      <c r="M47" s="78"/>
+      <c r="N47" s="78"/>
+      <c r="O47" s="78"/>
+      <c r="P47" s="78"/>
+      <c r="Q47" s="78"/>
+      <c r="R47" s="78"/>
+      <c r="S47" s="78"/>
+      <c r="T47" s="78"/>
     </row>
   </sheetData>
   <mergeCells count="81">
-    <mergeCell ref="B47:T47"/>
-    <mergeCell ref="B39:H39"/>
-    <mergeCell ref="I39:L39"/>
-    <mergeCell ref="M39:S39"/>
-    <mergeCell ref="D43:K43"/>
-    <mergeCell ref="M42:N42"/>
-    <mergeCell ref="O42:S42"/>
-    <mergeCell ref="M43:N43"/>
-    <mergeCell ref="O43:R43"/>
-    <mergeCell ref="B46:S46"/>
-    <mergeCell ref="I45:S45"/>
-    <mergeCell ref="H44:K44"/>
-    <mergeCell ref="M41:N41"/>
-    <mergeCell ref="O41:S41"/>
-    <mergeCell ref="B38:H38"/>
-    <mergeCell ref="I38:L38"/>
-    <mergeCell ref="M38:S38"/>
-    <mergeCell ref="J31:M31"/>
-    <mergeCell ref="J33:M33"/>
-    <mergeCell ref="J32:M32"/>
-    <mergeCell ref="J34:M34"/>
-    <mergeCell ref="Q31:S31"/>
-    <mergeCell ref="N35:P35"/>
-    <mergeCell ref="Q35:S35"/>
-    <mergeCell ref="J35:M35"/>
-    <mergeCell ref="I36:S36"/>
-    <mergeCell ref="B37:H37"/>
-    <mergeCell ref="I37:L37"/>
-    <mergeCell ref="M37:S37"/>
-    <mergeCell ref="N29:P29"/>
-    <mergeCell ref="Q29:S29"/>
-    <mergeCell ref="J29:M29"/>
-    <mergeCell ref="N31:P31"/>
-    <mergeCell ref="Q34:S34"/>
-    <mergeCell ref="N34:P34"/>
-    <mergeCell ref="Q33:S33"/>
-    <mergeCell ref="N33:P33"/>
-    <mergeCell ref="Q32:S32"/>
-    <mergeCell ref="N32:P32"/>
-    <mergeCell ref="J30:M30"/>
-    <mergeCell ref="N30:P30"/>
-    <mergeCell ref="Q30:S30"/>
-    <mergeCell ref="N28:P28"/>
-    <mergeCell ref="Q28:S28"/>
-    <mergeCell ref="Q27:S27"/>
-    <mergeCell ref="L25:M25"/>
-    <mergeCell ref="C26:I26"/>
-    <mergeCell ref="J28:M28"/>
-    <mergeCell ref="Q25:S25"/>
-    <mergeCell ref="L27:M27"/>
-    <mergeCell ref="C27:I27"/>
-    <mergeCell ref="K15:S15"/>
-    <mergeCell ref="C25:I25"/>
-    <mergeCell ref="L26:M26"/>
-    <mergeCell ref="Q26:S26"/>
-    <mergeCell ref="Q5:S5"/>
-    <mergeCell ref="H7:N7"/>
-    <mergeCell ref="I17:S17"/>
-    <mergeCell ref="Q7:S7"/>
-    <mergeCell ref="G11:S11"/>
-    <mergeCell ref="G12:S12"/>
-    <mergeCell ref="G13:S13"/>
-    <mergeCell ref="G14:J14"/>
-    <mergeCell ref="G15:J15"/>
-    <mergeCell ref="P22:R22"/>
     <mergeCell ref="Q2:S2"/>
     <mergeCell ref="D20:S20"/>
     <mergeCell ref="L24:M24"/>
@@ -2943,6 +2878,71 @@
     <mergeCell ref="F22:I22"/>
     <mergeCell ref="H8:N8"/>
     <mergeCell ref="O5:P5"/>
+    <mergeCell ref="K15:S15"/>
+    <mergeCell ref="C25:I25"/>
+    <mergeCell ref="L26:M26"/>
+    <mergeCell ref="Q26:S26"/>
+    <mergeCell ref="Q5:S5"/>
+    <mergeCell ref="H7:N7"/>
+    <mergeCell ref="I17:S17"/>
+    <mergeCell ref="Q7:S7"/>
+    <mergeCell ref="G11:S11"/>
+    <mergeCell ref="G12:S12"/>
+    <mergeCell ref="G13:S13"/>
+    <mergeCell ref="G14:J14"/>
+    <mergeCell ref="G15:J15"/>
+    <mergeCell ref="P22:R22"/>
+    <mergeCell ref="N28:P28"/>
+    <mergeCell ref="Q28:S28"/>
+    <mergeCell ref="Q27:S27"/>
+    <mergeCell ref="L25:M25"/>
+    <mergeCell ref="C26:I26"/>
+    <mergeCell ref="J28:M28"/>
+    <mergeCell ref="Q25:S25"/>
+    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="C27:I27"/>
+    <mergeCell ref="N29:P29"/>
+    <mergeCell ref="Q29:S29"/>
+    <mergeCell ref="J29:M29"/>
+    <mergeCell ref="N31:P31"/>
+    <mergeCell ref="Q34:S34"/>
+    <mergeCell ref="N34:P34"/>
+    <mergeCell ref="Q33:S33"/>
+    <mergeCell ref="N33:P33"/>
+    <mergeCell ref="Q32:S32"/>
+    <mergeCell ref="N32:P32"/>
+    <mergeCell ref="J30:M30"/>
+    <mergeCell ref="N30:P30"/>
+    <mergeCell ref="Q30:S30"/>
+    <mergeCell ref="B38:H38"/>
+    <mergeCell ref="I38:L38"/>
+    <mergeCell ref="M38:S38"/>
+    <mergeCell ref="J31:M31"/>
+    <mergeCell ref="J33:M33"/>
+    <mergeCell ref="J32:M32"/>
+    <mergeCell ref="J34:M34"/>
+    <mergeCell ref="Q31:S31"/>
+    <mergeCell ref="N35:P35"/>
+    <mergeCell ref="Q35:S35"/>
+    <mergeCell ref="J35:M35"/>
+    <mergeCell ref="I36:S36"/>
+    <mergeCell ref="B37:H37"/>
+    <mergeCell ref="I37:L37"/>
+    <mergeCell ref="M37:S37"/>
+    <mergeCell ref="B47:T47"/>
+    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="I39:L39"/>
+    <mergeCell ref="M39:S39"/>
+    <mergeCell ref="D43:K43"/>
+    <mergeCell ref="M42:N42"/>
+    <mergeCell ref="O42:S42"/>
+    <mergeCell ref="M43:N43"/>
+    <mergeCell ref="O43:R43"/>
+    <mergeCell ref="B46:S46"/>
+    <mergeCell ref="I45:S45"/>
+    <mergeCell ref="H44:K44"/>
+    <mergeCell ref="M41:N41"/>
+    <mergeCell ref="O41:S41"/>
   </mergeCells>
   <pageMargins left="0.3" right="0" top="0.5" bottom="0" header="0.5" footer="0"/>
   <pageSetup paperSize="9" scale="91" orientation="portrait" r:id="rId1"/>

--- a/resources/report/60/95/ex_imp/TID_122_VAT INVOICE_MULTI_IMP.xlsx
+++ b/resources/report/60/95/ex_imp/TID_122_VAT INVOICE_MULTI_IMP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\einvoicevn\resources\report\60\95\ex_imp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3430A37D-7E18-416C-A6B4-4E4E344B1458}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9826C94B-1B8A-4DC5-9626-E09E0F2DA087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="754" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1331,12 +1331,159 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1346,6 +1493,12 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1373,161 +1526,8 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1843,22 +1843,22 @@
       <c r="E2" s="22"/>
       <c r="F2" s="22"/>
       <c r="G2" s="22"/>
-      <c r="H2" s="136" t="s">
+      <c r="H2" s="83" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="136"/>
-      <c r="J2" s="136"/>
-      <c r="K2" s="136"/>
-      <c r="L2" s="136"/>
-      <c r="M2" s="136"/>
-      <c r="N2" s="136"/>
-      <c r="O2" s="140" t="s">
+      <c r="I2" s="83"/>
+      <c r="J2" s="83"/>
+      <c r="K2" s="83"/>
+      <c r="L2" s="83"/>
+      <c r="M2" s="83"/>
+      <c r="N2" s="83"/>
+      <c r="O2" s="88" t="s">
         <v>45</v>
       </c>
-      <c r="P2" s="140"/>
-      <c r="Q2" s="131"/>
-      <c r="R2" s="131"/>
-      <c r="S2" s="131"/>
+      <c r="P2" s="88"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="78"/>
       <c r="T2" s="23"/>
     </row>
     <row r="3" spans="1:20" s="7" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -1869,13 +1869,13 @@
       <c r="E3" s="9"/>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
-      <c r="H3" s="137"/>
-      <c r="I3" s="137"/>
-      <c r="J3" s="137"/>
-      <c r="K3" s="137"/>
-      <c r="L3" s="137"/>
-      <c r="M3" s="137"/>
-      <c r="N3" s="137"/>
+      <c r="H3" s="84"/>
+      <c r="I3" s="84"/>
+      <c r="J3" s="84"/>
+      <c r="K3" s="84"/>
+      <c r="L3" s="84"/>
+      <c r="M3" s="84"/>
+      <c r="N3" s="84"/>
       <c r="O3" s="50"/>
       <c r="P3" s="50"/>
       <c r="Q3" s="57"/>
@@ -1891,13 +1891,13 @@
       <c r="E4" s="9"/>
       <c r="F4" s="9"/>
       <c r="G4" s="9"/>
-      <c r="H4" s="137"/>
-      <c r="I4" s="137"/>
-      <c r="J4" s="137"/>
-      <c r="K4" s="137"/>
-      <c r="L4" s="137"/>
-      <c r="M4" s="137"/>
-      <c r="N4" s="137"/>
+      <c r="H4" s="84"/>
+      <c r="I4" s="84"/>
+      <c r="J4" s="84"/>
+      <c r="K4" s="84"/>
+      <c r="L4" s="84"/>
+      <c r="M4" s="84"/>
+      <c r="N4" s="84"/>
       <c r="O4" s="18"/>
       <c r="P4" s="18"/>
       <c r="Q4" s="57"/>
@@ -1913,22 +1913,22 @@
       <c r="E5" s="9"/>
       <c r="F5" s="9"/>
       <c r="G5" s="9"/>
-      <c r="H5" s="139" t="s">
+      <c r="H5" s="86" t="s">
         <v>18</v>
       </c>
-      <c r="I5" s="139"/>
-      <c r="J5" s="139"/>
-      <c r="K5" s="139"/>
-      <c r="L5" s="139"/>
-      <c r="M5" s="139"/>
-      <c r="N5" s="139"/>
-      <c r="O5" s="138" t="s">
+      <c r="I5" s="86"/>
+      <c r="J5" s="86"/>
+      <c r="K5" s="86"/>
+      <c r="L5" s="86"/>
+      <c r="M5" s="86"/>
+      <c r="N5" s="86"/>
+      <c r="O5" s="85" t="s">
         <v>46</v>
       </c>
-      <c r="P5" s="138"/>
-      <c r="Q5" s="123"/>
-      <c r="R5" s="123"/>
-      <c r="S5" s="123"/>
+      <c r="P5" s="85"/>
+      <c r="Q5" s="98"/>
+      <c r="R5" s="98"/>
+      <c r="S5" s="98"/>
       <c r="T5" s="25"/>
     </row>
     <row r="6" spans="1:20" s="7" customFormat="1" ht="13.15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1939,13 +1939,13 @@
       <c r="E6" s="9"/>
       <c r="F6" s="9"/>
       <c r="G6" s="9"/>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
-      <c r="J6" s="79"/>
-      <c r="K6" s="79"/>
-      <c r="L6" s="79"/>
-      <c r="M6" s="79"/>
-      <c r="N6" s="79"/>
+      <c r="H6" s="87"/>
+      <c r="I6" s="87"/>
+      <c r="J6" s="87"/>
+      <c r="K6" s="87"/>
+      <c r="L6" s="87"/>
+      <c r="M6" s="87"/>
+      <c r="N6" s="87"/>
       <c r="O6" s="50"/>
       <c r="P6" s="50"/>
       <c r="Q6" s="57"/>
@@ -1961,20 +1961,20 @@
       <c r="E7" s="8"/>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
-      <c r="H7" s="124" t="s">
+      <c r="H7" s="99" t="s">
         <v>25</v>
       </c>
-      <c r="I7" s="124"/>
-      <c r="J7" s="124"/>
-      <c r="K7" s="124"/>
-      <c r="L7" s="124"/>
-      <c r="M7" s="124"/>
-      <c r="N7" s="124"/>
-      <c r="O7" s="138"/>
-      <c r="P7" s="138"/>
-      <c r="Q7" s="126"/>
-      <c r="R7" s="126"/>
-      <c r="S7" s="126"/>
+      <c r="I7" s="99"/>
+      <c r="J7" s="99"/>
+      <c r="K7" s="99"/>
+      <c r="L7" s="99"/>
+      <c r="M7" s="99"/>
+      <c r="N7" s="99"/>
+      <c r="O7" s="85"/>
+      <c r="P7" s="85"/>
+      <c r="Q7" s="101"/>
+      <c r="R7" s="101"/>
+      <c r="S7" s="101"/>
       <c r="T7" s="27"/>
     </row>
     <row r="8" spans="1:20" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -1985,13 +1985,13 @@
       <c r="E8" s="8"/>
       <c r="F8" s="11"/>
       <c r="G8" s="11"/>
-      <c r="H8" s="141"/>
-      <c r="I8" s="141"/>
-      <c r="J8" s="141"/>
-      <c r="K8" s="141"/>
-      <c r="L8" s="141"/>
-      <c r="M8" s="141"/>
-      <c r="N8" s="141"/>
+      <c r="H8" s="90"/>
+      <c r="I8" s="90"/>
+      <c r="J8" s="90"/>
+      <c r="K8" s="90"/>
+      <c r="L8" s="90"/>
+      <c r="M8" s="90"/>
+      <c r="N8" s="90"/>
       <c r="O8" s="62"/>
       <c r="P8" s="62"/>
       <c r="Q8" s="62"/>
@@ -2036,19 +2036,19 @@
       <c r="F11" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G11" s="127"/>
-      <c r="H11" s="127"/>
-      <c r="I11" s="127"/>
-      <c r="J11" s="127"/>
-      <c r="K11" s="127"/>
-      <c r="L11" s="127"/>
-      <c r="M11" s="127"/>
-      <c r="N11" s="127"/>
-      <c r="O11" s="127"/>
-      <c r="P11" s="127"/>
-      <c r="Q11" s="127"/>
-      <c r="R11" s="127"/>
-      <c r="S11" s="127"/>
+      <c r="G11" s="102"/>
+      <c r="H11" s="102"/>
+      <c r="I11" s="102"/>
+      <c r="J11" s="102"/>
+      <c r="K11" s="102"/>
+      <c r="L11" s="102"/>
+      <c r="M11" s="102"/>
+      <c r="N11" s="102"/>
+      <c r="O11" s="102"/>
+      <c r="P11" s="102"/>
+      <c r="Q11" s="102"/>
+      <c r="R11" s="102"/>
+      <c r="S11" s="102"/>
       <c r="T11" s="28"/>
     </row>
     <row r="12" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -2062,19 +2062,19 @@
       <c r="F12" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G12" s="128"/>
-      <c r="H12" s="128"/>
-      <c r="I12" s="128"/>
-      <c r="J12" s="128"/>
-      <c r="K12" s="128"/>
-      <c r="L12" s="128"/>
-      <c r="M12" s="128"/>
-      <c r="N12" s="128"/>
-      <c r="O12" s="128"/>
-      <c r="P12" s="128"/>
-      <c r="Q12" s="128"/>
-      <c r="R12" s="128"/>
-      <c r="S12" s="128"/>
+      <c r="G12" s="103"/>
+      <c r="H12" s="103"/>
+      <c r="I12" s="103"/>
+      <c r="J12" s="103"/>
+      <c r="K12" s="103"/>
+      <c r="L12" s="103"/>
+      <c r="M12" s="103"/>
+      <c r="N12" s="103"/>
+      <c r="O12" s="103"/>
+      <c r="P12" s="103"/>
+      <c r="Q12" s="103"/>
+      <c r="R12" s="103"/>
+      <c r="S12" s="103"/>
       <c r="T12" s="28"/>
     </row>
     <row r="13" spans="1:20" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -2088,19 +2088,19 @@
       <c r="F13" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G13" s="129"/>
-      <c r="H13" s="129"/>
-      <c r="I13" s="129"/>
-      <c r="J13" s="129"/>
-      <c r="K13" s="129"/>
-      <c r="L13" s="129"/>
-      <c r="M13" s="129"/>
-      <c r="N13" s="129"/>
-      <c r="O13" s="129"/>
-      <c r="P13" s="129"/>
-      <c r="Q13" s="129"/>
-      <c r="R13" s="129"/>
-      <c r="S13" s="129"/>
+      <c r="G13" s="104"/>
+      <c r="H13" s="104"/>
+      <c r="I13" s="104"/>
+      <c r="J13" s="104"/>
+      <c r="K13" s="104"/>
+      <c r="L13" s="104"/>
+      <c r="M13" s="104"/>
+      <c r="N13" s="104"/>
+      <c r="O13" s="104"/>
+      <c r="P13" s="104"/>
+      <c r="Q13" s="104"/>
+      <c r="R13" s="104"/>
+      <c r="S13" s="104"/>
       <c r="T13" s="28"/>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.35">
@@ -2112,10 +2112,10 @@
       <c r="F14" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G14" s="130"/>
-      <c r="H14" s="130"/>
-      <c r="I14" s="130"/>
-      <c r="J14" s="130"/>
+      <c r="G14" s="89"/>
+      <c r="H14" s="89"/>
+      <c r="I14" s="89"/>
+      <c r="J14" s="89"/>
       <c r="K14" s="16"/>
       <c r="L14" s="16"/>
       <c r="M14" s="16"/>
@@ -2136,19 +2136,19 @@
       <c r="F15" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G15" s="130"/>
-      <c r="H15" s="130"/>
-      <c r="I15" s="130"/>
-      <c r="J15" s="130"/>
-      <c r="K15" s="122"/>
-      <c r="L15" s="122"/>
-      <c r="M15" s="122"/>
-      <c r="N15" s="122"/>
-      <c r="O15" s="122"/>
-      <c r="P15" s="122"/>
-      <c r="Q15" s="122"/>
-      <c r="R15" s="122"/>
-      <c r="S15" s="122"/>
+      <c r="G15" s="89"/>
+      <c r="H15" s="89"/>
+      <c r="I15" s="89"/>
+      <c r="J15" s="89"/>
+      <c r="K15" s="91"/>
+      <c r="L15" s="91"/>
+      <c r="M15" s="91"/>
+      <c r="N15" s="91"/>
+      <c r="O15" s="91"/>
+      <c r="P15" s="91"/>
+      <c r="Q15" s="91"/>
+      <c r="R15" s="91"/>
+      <c r="S15" s="91"/>
       <c r="T15" s="28"/>
     </row>
     <row r="16" spans="1:20" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.35">
@@ -2178,17 +2178,17 @@
       <c r="B17" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="I17" s="125"/>
-      <c r="J17" s="125"/>
-      <c r="K17" s="125"/>
-      <c r="L17" s="125"/>
-      <c r="M17" s="125"/>
-      <c r="N17" s="125"/>
-      <c r="O17" s="125"/>
-      <c r="P17" s="125"/>
-      <c r="Q17" s="125"/>
-      <c r="R17" s="125"/>
-      <c r="S17" s="125"/>
+      <c r="I17" s="100"/>
+      <c r="J17" s="100"/>
+      <c r="K17" s="100"/>
+      <c r="L17" s="100"/>
+      <c r="M17" s="100"/>
+      <c r="N17" s="100"/>
+      <c r="O17" s="100"/>
+      <c r="P17" s="100"/>
+      <c r="Q17" s="100"/>
+      <c r="R17" s="100"/>
+      <c r="S17" s="100"/>
       <c r="T17" s="30"/>
     </row>
     <row r="18" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2196,18 +2196,18 @@
       <c r="B18" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="H18" s="130"/>
-      <c r="I18" s="130"/>
-      <c r="J18" s="130"/>
-      <c r="K18" s="130"/>
-      <c r="L18" s="130"/>
-      <c r="M18" s="130"/>
-      <c r="N18" s="130"/>
-      <c r="O18" s="130"/>
-      <c r="P18" s="130"/>
-      <c r="Q18" s="130"/>
-      <c r="R18" s="130"/>
-      <c r="S18" s="130"/>
+      <c r="H18" s="89"/>
+      <c r="I18" s="89"/>
+      <c r="J18" s="89"/>
+      <c r="K18" s="89"/>
+      <c r="L18" s="89"/>
+      <c r="M18" s="89"/>
+      <c r="N18" s="89"/>
+      <c r="O18" s="89"/>
+      <c r="P18" s="89"/>
+      <c r="Q18" s="89"/>
+      <c r="R18" s="89"/>
+      <c r="S18" s="89"/>
       <c r="T18" s="30"/>
     </row>
     <row r="19" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2215,11 +2215,11 @@
       <c r="B19" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E19" s="130"/>
-      <c r="F19" s="130"/>
-      <c r="G19" s="130"/>
-      <c r="H19" s="130"/>
-      <c r="I19" s="130"/>
+      <c r="E19" s="89"/>
+      <c r="F19" s="89"/>
+      <c r="G19" s="89"/>
+      <c r="H19" s="89"/>
+      <c r="I19" s="89"/>
       <c r="T19" s="30"/>
     </row>
     <row r="20" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2227,22 +2227,22 @@
       <c r="B20" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D20" s="132"/>
-      <c r="E20" s="132"/>
-      <c r="F20" s="132"/>
-      <c r="G20" s="132"/>
-      <c r="H20" s="132"/>
-      <c r="I20" s="132"/>
-      <c r="J20" s="132"/>
-      <c r="K20" s="132"/>
-      <c r="L20" s="132"/>
-      <c r="M20" s="132"/>
-      <c r="N20" s="132"/>
-      <c r="O20" s="132"/>
-      <c r="P20" s="132"/>
-      <c r="Q20" s="132"/>
-      <c r="R20" s="132"/>
-      <c r="S20" s="132"/>
+      <c r="D20" s="79"/>
+      <c r="E20" s="79"/>
+      <c r="F20" s="79"/>
+      <c r="G20" s="79"/>
+      <c r="H20" s="79"/>
+      <c r="I20" s="79"/>
+      <c r="J20" s="79"/>
+      <c r="K20" s="79"/>
+      <c r="L20" s="79"/>
+      <c r="M20" s="79"/>
+      <c r="N20" s="79"/>
+      <c r="O20" s="79"/>
+      <c r="P20" s="79"/>
+      <c r="Q20" s="79"/>
+      <c r="R20" s="79"/>
+      <c r="S20" s="79"/>
       <c r="T20" s="30"/>
     </row>
     <row r="21" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2256,9 +2256,9 @@
       <c r="G21" s="55"/>
       <c r="H21" s="55"/>
       <c r="I21" s="55"/>
-      <c r="J21" s="132"/>
-      <c r="K21" s="132"/>
-      <c r="L21" s="132"/>
+      <c r="J21" s="79"/>
+      <c r="K21" s="79"/>
+      <c r="L21" s="79"/>
       <c r="M21" s="55"/>
       <c r="N21" s="55"/>
       <c r="O21" s="55"/>
@@ -2273,16 +2273,16 @@
       <c r="B22" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F22" s="130"/>
-      <c r="G22" s="130"/>
-      <c r="H22" s="130"/>
-      <c r="I22" s="130"/>
+      <c r="F22" s="89"/>
+      <c r="G22" s="89"/>
+      <c r="H22" s="89"/>
+      <c r="I22" s="89"/>
       <c r="M22" s="56" t="s">
         <v>50</v>
       </c>
-      <c r="P22" s="124"/>
-      <c r="Q22" s="124"/>
-      <c r="R22" s="124"/>
+      <c r="P22" s="99"/>
+      <c r="Q22" s="99"/>
+      <c r="R22" s="99"/>
       <c r="T22" s="30"/>
     </row>
     <row r="23" spans="1:20" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.35">
@@ -2294,25 +2294,25 @@
       <c r="B24" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="C24" s="133" t="s">
+      <c r="C24" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="D24" s="135"/>
-      <c r="E24" s="135"/>
-      <c r="F24" s="135"/>
-      <c r="G24" s="135"/>
-      <c r="H24" s="135"/>
-      <c r="I24" s="134"/>
+      <c r="D24" s="82"/>
+      <c r="E24" s="82"/>
+      <c r="F24" s="82"/>
+      <c r="G24" s="82"/>
+      <c r="H24" s="82"/>
+      <c r="I24" s="81"/>
       <c r="J24" s="40" t="s">
         <v>3</v>
       </c>
       <c r="K24" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="L24" s="133" t="s">
+      <c r="L24" s="80" t="s">
         <v>13</v>
       </c>
-      <c r="M24" s="134"/>
+      <c r="M24" s="81"/>
       <c r="N24" s="40" t="s">
         <v>2</v>
       </c>
@@ -2322,11 +2322,11 @@
       <c r="P24" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="Q24" s="133" t="s">
+      <c r="Q24" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="R24" s="135"/>
-      <c r="S24" s="134"/>
+      <c r="R24" s="82"/>
+      <c r="S24" s="81"/>
       <c r="T24" s="42"/>
     </row>
     <row r="25" spans="1:20" s="47" customFormat="1" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2334,25 +2334,25 @@
       <c r="B25" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="115" t="s">
+      <c r="C25" s="92" t="s">
         <v>7</v>
       </c>
-      <c r="D25" s="120"/>
-      <c r="E25" s="120"/>
-      <c r="F25" s="120"/>
-      <c r="G25" s="120"/>
-      <c r="H25" s="120"/>
-      <c r="I25" s="116"/>
+      <c r="D25" s="93"/>
+      <c r="E25" s="93"/>
+      <c r="F25" s="93"/>
+      <c r="G25" s="93"/>
+      <c r="H25" s="93"/>
+      <c r="I25" s="94"/>
       <c r="J25" s="45" t="s">
         <v>8</v>
       </c>
       <c r="K25" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="L25" s="115" t="s">
+      <c r="L25" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="M25" s="116"/>
+      <c r="M25" s="94"/>
       <c r="N25" s="45" t="s">
         <v>9</v>
       </c>
@@ -2362,11 +2362,11 @@
       <c r="P25" s="53" t="s">
         <v>33</v>
       </c>
-      <c r="Q25" s="115" t="s">
+      <c r="Q25" s="92" t="s">
         <v>34</v>
       </c>
-      <c r="R25" s="120"/>
-      <c r="S25" s="116"/>
+      <c r="R25" s="93"/>
+      <c r="S25" s="94"/>
       <c r="T25" s="46"/>
     </row>
     <row r="26" spans="1:20" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.3">
@@ -2374,25 +2374,25 @@
       <c r="B26" s="4">
         <v>1</v>
       </c>
-      <c r="C26" s="117">
+      <c r="C26" s="95">
         <v>2</v>
       </c>
-      <c r="D26" s="118"/>
-      <c r="E26" s="118"/>
-      <c r="F26" s="118"/>
-      <c r="G26" s="118"/>
-      <c r="H26" s="118"/>
-      <c r="I26" s="119"/>
+      <c r="D26" s="97"/>
+      <c r="E26" s="97"/>
+      <c r="F26" s="97"/>
+      <c r="G26" s="97"/>
+      <c r="H26" s="97"/>
+      <c r="I26" s="96"/>
       <c r="J26" s="4">
         <v>3</v>
       </c>
       <c r="K26" s="4">
         <v>4</v>
       </c>
-      <c r="L26" s="117">
+      <c r="L26" s="95">
         <v>5</v>
       </c>
-      <c r="M26" s="119"/>
+      <c r="M26" s="96"/>
       <c r="N26" s="4" t="s">
         <v>19</v>
       </c>
@@ -2402,33 +2402,33 @@
       <c r="P26" s="37">
         <v>8</v>
       </c>
-      <c r="Q26" s="117" t="s">
+      <c r="Q26" s="95" t="s">
         <v>29</v>
       </c>
-      <c r="R26" s="118"/>
-      <c r="S26" s="119"/>
+      <c r="R26" s="97"/>
+      <c r="S26" s="96"/>
       <c r="T26" s="58"/>
     </row>
     <row r="27" spans="1:20" s="11" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="33"/>
       <c r="B27" s="72"/>
-      <c r="C27" s="121"/>
-      <c r="D27" s="121"/>
-      <c r="E27" s="121"/>
-      <c r="F27" s="121"/>
-      <c r="G27" s="121"/>
-      <c r="H27" s="121"/>
-      <c r="I27" s="121"/>
+      <c r="C27" s="143"/>
+      <c r="D27" s="143"/>
+      <c r="E27" s="143"/>
+      <c r="F27" s="143"/>
+      <c r="G27" s="143"/>
+      <c r="H27" s="143"/>
+      <c r="I27" s="143"/>
       <c r="J27" s="72"/>
       <c r="K27" s="73"/>
-      <c r="L27" s="112"/>
-      <c r="M27" s="114"/>
+      <c r="L27" s="108"/>
+      <c r="M27" s="110"/>
       <c r="N27" s="73"/>
       <c r="O27" s="74"/>
       <c r="P27" s="75"/>
-      <c r="Q27" s="112"/>
-      <c r="R27" s="113"/>
-      <c r="S27" s="114"/>
+      <c r="Q27" s="108"/>
+      <c r="R27" s="109"/>
+      <c r="S27" s="110"/>
       <c r="T27" s="59"/>
     </row>
     <row r="28" spans="1:20" s="50" customFormat="1" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
@@ -2441,22 +2441,22 @@
       <c r="G28" s="65"/>
       <c r="H28" s="65"/>
       <c r="I28" s="66"/>
-      <c r="J28" s="109" t="s">
+      <c r="J28" s="105" t="s">
         <v>37</v>
       </c>
-      <c r="K28" s="110"/>
-      <c r="L28" s="110"/>
-      <c r="M28" s="111"/>
-      <c r="N28" s="109" t="s">
+      <c r="K28" s="106"/>
+      <c r="L28" s="106"/>
+      <c r="M28" s="107"/>
+      <c r="N28" s="105" t="s">
         <v>28</v>
       </c>
-      <c r="O28" s="110"/>
-      <c r="P28" s="111"/>
-      <c r="Q28" s="109" t="s">
+      <c r="O28" s="106"/>
+      <c r="P28" s="107"/>
+      <c r="Q28" s="105" t="s">
         <v>47</v>
       </c>
-      <c r="R28" s="110"/>
-      <c r="S28" s="111"/>
+      <c r="R28" s="106"/>
+      <c r="S28" s="107"/>
       <c r="T28" s="60"/>
     </row>
     <row r="29" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2471,16 +2471,16 @@
       <c r="G29" s="12"/>
       <c r="H29" s="12"/>
       <c r="I29" s="12"/>
-      <c r="J29" s="94"/>
-      <c r="K29" s="95"/>
-      <c r="L29" s="95"/>
-      <c r="M29" s="96"/>
-      <c r="N29" s="97"/>
-      <c r="O29" s="98"/>
-      <c r="P29" s="99"/>
-      <c r="Q29" s="97"/>
-      <c r="R29" s="98"/>
-      <c r="S29" s="99"/>
+      <c r="J29" s="114"/>
+      <c r="K29" s="115"/>
+      <c r="L29" s="115"/>
+      <c r="M29" s="116"/>
+      <c r="N29" s="111"/>
+      <c r="O29" s="112"/>
+      <c r="P29" s="113"/>
+      <c r="Q29" s="111"/>
+      <c r="R29" s="112"/>
+      <c r="S29" s="113"/>
       <c r="T29" s="67"/>
     </row>
     <row r="30" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2495,16 +2495,16 @@
       <c r="G30" s="12"/>
       <c r="H30" s="12"/>
       <c r="I30" s="12"/>
-      <c r="J30" s="94"/>
-      <c r="K30" s="95"/>
-      <c r="L30" s="95"/>
-      <c r="M30" s="96"/>
-      <c r="N30" s="97"/>
-      <c r="O30" s="98"/>
-      <c r="P30" s="99"/>
-      <c r="Q30" s="97"/>
-      <c r="R30" s="98"/>
-      <c r="S30" s="99"/>
+      <c r="J30" s="114"/>
+      <c r="K30" s="115"/>
+      <c r="L30" s="115"/>
+      <c r="M30" s="116"/>
+      <c r="N30" s="111"/>
+      <c r="O30" s="112"/>
+      <c r="P30" s="113"/>
+      <c r="Q30" s="111"/>
+      <c r="R30" s="112"/>
+      <c r="S30" s="113"/>
       <c r="T30" s="67"/>
     </row>
     <row r="31" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2519,16 +2519,16 @@
       <c r="G31" s="12"/>
       <c r="H31" s="12"/>
       <c r="I31" s="12"/>
-      <c r="J31" s="94"/>
-      <c r="K31" s="95"/>
-      <c r="L31" s="95"/>
-      <c r="M31" s="96"/>
-      <c r="N31" s="97"/>
-      <c r="O31" s="98"/>
-      <c r="P31" s="99"/>
-      <c r="Q31" s="97"/>
-      <c r="R31" s="98"/>
-      <c r="S31" s="99"/>
+      <c r="J31" s="114"/>
+      <c r="K31" s="115"/>
+      <c r="L31" s="115"/>
+      <c r="M31" s="116"/>
+      <c r="N31" s="111"/>
+      <c r="O31" s="112"/>
+      <c r="P31" s="113"/>
+      <c r="Q31" s="111"/>
+      <c r="R31" s="112"/>
+      <c r="S31" s="113"/>
       <c r="T31" s="67"/>
     </row>
     <row r="32" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2543,16 +2543,16 @@
       <c r="G32" s="12"/>
       <c r="H32" s="12"/>
       <c r="I32" s="12"/>
-      <c r="J32" s="94"/>
-      <c r="K32" s="95"/>
-      <c r="L32" s="95"/>
-      <c r="M32" s="96"/>
-      <c r="N32" s="97"/>
-      <c r="O32" s="98"/>
-      <c r="P32" s="99"/>
-      <c r="Q32" s="97"/>
-      <c r="R32" s="98"/>
-      <c r="S32" s="99"/>
+      <c r="J32" s="114"/>
+      <c r="K32" s="115"/>
+      <c r="L32" s="115"/>
+      <c r="M32" s="116"/>
+      <c r="N32" s="111"/>
+      <c r="O32" s="112"/>
+      <c r="P32" s="113"/>
+      <c r="Q32" s="111"/>
+      <c r="R32" s="112"/>
+      <c r="S32" s="113"/>
       <c r="T32" s="67"/>
     </row>
     <row r="33" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2567,16 +2567,16 @@
       <c r="G33" s="12"/>
       <c r="H33" s="12"/>
       <c r="I33" s="12"/>
-      <c r="J33" s="94"/>
-      <c r="K33" s="95"/>
-      <c r="L33" s="95"/>
-      <c r="M33" s="96"/>
-      <c r="N33" s="97"/>
-      <c r="O33" s="98"/>
-      <c r="P33" s="99"/>
-      <c r="Q33" s="97"/>
-      <c r="R33" s="98"/>
-      <c r="S33" s="99"/>
+      <c r="J33" s="114"/>
+      <c r="K33" s="115"/>
+      <c r="L33" s="115"/>
+      <c r="M33" s="116"/>
+      <c r="N33" s="111"/>
+      <c r="O33" s="112"/>
+      <c r="P33" s="113"/>
+      <c r="Q33" s="111"/>
+      <c r="R33" s="112"/>
+      <c r="S33" s="113"/>
       <c r="T33" s="67"/>
     </row>
     <row r="34" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2591,16 +2591,16 @@
       <c r="G34" s="12"/>
       <c r="H34" s="12"/>
       <c r="I34" s="12"/>
-      <c r="J34" s="94"/>
-      <c r="K34" s="95"/>
-      <c r="L34" s="95"/>
-      <c r="M34" s="96"/>
-      <c r="N34" s="97"/>
-      <c r="O34" s="98"/>
-      <c r="P34" s="99"/>
-      <c r="Q34" s="97"/>
-      <c r="R34" s="98"/>
-      <c r="S34" s="99"/>
+      <c r="J34" s="114"/>
+      <c r="K34" s="115"/>
+      <c r="L34" s="115"/>
+      <c r="M34" s="116"/>
+      <c r="N34" s="111"/>
+      <c r="O34" s="112"/>
+      <c r="P34" s="113"/>
+      <c r="Q34" s="111"/>
+      <c r="R34" s="112"/>
+      <c r="S34" s="113"/>
       <c r="T34" s="67"/>
     </row>
     <row r="35" spans="1:20" s="2" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -2615,16 +2615,16 @@
       <c r="G35" s="12"/>
       <c r="H35" s="12"/>
       <c r="I35" s="12"/>
-      <c r="J35" s="100"/>
-      <c r="K35" s="101"/>
-      <c r="L35" s="101"/>
-      <c r="M35" s="102"/>
-      <c r="N35" s="100"/>
-      <c r="O35" s="101"/>
-      <c r="P35" s="102"/>
-      <c r="Q35" s="103"/>
-      <c r="R35" s="104"/>
-      <c r="S35" s="105"/>
+      <c r="J35" s="119"/>
+      <c r="K35" s="120"/>
+      <c r="L35" s="120"/>
+      <c r="M35" s="121"/>
+      <c r="N35" s="119"/>
+      <c r="O35" s="120"/>
+      <c r="P35" s="121"/>
+      <c r="Q35" s="122"/>
+      <c r="R35" s="123"/>
+      <c r="S35" s="124"/>
       <c r="T35" s="67"/>
     </row>
     <row r="36" spans="1:20" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2638,95 +2638,95 @@
       <c r="F36" s="12"/>
       <c r="G36" s="12"/>
       <c r="H36" s="12"/>
-      <c r="I36" s="106"/>
-      <c r="J36" s="106"/>
-      <c r="K36" s="106"/>
-      <c r="L36" s="106"/>
-      <c r="M36" s="106"/>
-      <c r="N36" s="106"/>
-      <c r="O36" s="106"/>
-      <c r="P36" s="106"/>
-      <c r="Q36" s="106"/>
-      <c r="R36" s="106"/>
-      <c r="S36" s="107"/>
+      <c r="I36" s="125"/>
+      <c r="J36" s="125"/>
+      <c r="K36" s="125"/>
+      <c r="L36" s="125"/>
+      <c r="M36" s="125"/>
+      <c r="N36" s="125"/>
+      <c r="O36" s="125"/>
+      <c r="P36" s="125"/>
+      <c r="Q36" s="125"/>
+      <c r="R36" s="125"/>
+      <c r="S36" s="126"/>
       <c r="T36" s="67"/>
     </row>
     <row r="37" spans="1:20" s="10" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="34"/>
-      <c r="B37" s="108" t="s">
+      <c r="B37" s="127" t="s">
         <v>17</v>
       </c>
-      <c r="C37" s="108"/>
-      <c r="D37" s="108"/>
-      <c r="E37" s="108"/>
-      <c r="F37" s="108"/>
-      <c r="G37" s="108"/>
-      <c r="H37" s="108"/>
-      <c r="I37" s="108"/>
-      <c r="J37" s="108"/>
-      <c r="K37" s="108"/>
-      <c r="L37" s="108"/>
-      <c r="M37" s="108" t="s">
+      <c r="C37" s="127"/>
+      <c r="D37" s="127"/>
+      <c r="E37" s="127"/>
+      <c r="F37" s="127"/>
+      <c r="G37" s="127"/>
+      <c r="H37" s="127"/>
+      <c r="I37" s="127"/>
+      <c r="J37" s="127"/>
+      <c r="K37" s="127"/>
+      <c r="L37" s="127"/>
+      <c r="M37" s="127" t="s">
         <v>14</v>
       </c>
-      <c r="N37" s="108"/>
-      <c r="O37" s="108"/>
-      <c r="P37" s="108"/>
-      <c r="Q37" s="108"/>
-      <c r="R37" s="108"/>
-      <c r="S37" s="108"/>
+      <c r="N37" s="127"/>
+      <c r="O37" s="127"/>
+      <c r="P37" s="127"/>
+      <c r="Q37" s="127"/>
+      <c r="R37" s="127"/>
+      <c r="S37" s="127"/>
       <c r="T37" s="35"/>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A38" s="26"/>
-      <c r="B38" s="92" t="s">
+      <c r="B38" s="117" t="s">
         <v>11</v>
       </c>
-      <c r="C38" s="92"/>
-      <c r="D38" s="92"/>
-      <c r="E38" s="92"/>
-      <c r="F38" s="92"/>
-      <c r="G38" s="92"/>
-      <c r="H38" s="92"/>
-      <c r="I38" s="93"/>
-      <c r="J38" s="93"/>
-      <c r="K38" s="93"/>
-      <c r="L38" s="93"/>
-      <c r="M38" s="93" t="s">
+      <c r="C38" s="117"/>
+      <c r="D38" s="117"/>
+      <c r="E38" s="117"/>
+      <c r="F38" s="117"/>
+      <c r="G38" s="117"/>
+      <c r="H38" s="117"/>
+      <c r="I38" s="118"/>
+      <c r="J38" s="118"/>
+      <c r="K38" s="118"/>
+      <c r="L38" s="118"/>
+      <c r="M38" s="118" t="s">
         <v>57</v>
       </c>
-      <c r="N38" s="93"/>
-      <c r="O38" s="93"/>
-      <c r="P38" s="93"/>
-      <c r="Q38" s="93"/>
-      <c r="R38" s="93"/>
-      <c r="S38" s="93"/>
+      <c r="N38" s="118"/>
+      <c r="O38" s="118"/>
+      <c r="P38" s="118"/>
+      <c r="Q38" s="118"/>
+      <c r="R38" s="118"/>
+      <c r="S38" s="118"/>
       <c r="T38" s="31"/>
     </row>
     <row r="39" spans="1:20" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="26"/>
-      <c r="B39" s="79" t="s">
+      <c r="B39" s="87" t="s">
         <v>12</v>
       </c>
-      <c r="C39" s="79"/>
-      <c r="D39" s="79"/>
-      <c r="E39" s="79"/>
-      <c r="F39" s="79"/>
-      <c r="G39" s="79"/>
-      <c r="H39" s="79"/>
-      <c r="I39" s="79"/>
-      <c r="J39" s="79"/>
-      <c r="K39" s="79"/>
-      <c r="L39" s="79"/>
-      <c r="M39" s="79" t="s">
+      <c r="C39" s="87"/>
+      <c r="D39" s="87"/>
+      <c r="E39" s="87"/>
+      <c r="F39" s="87"/>
+      <c r="G39" s="87"/>
+      <c r="H39" s="87"/>
+      <c r="I39" s="87"/>
+      <c r="J39" s="87"/>
+      <c r="K39" s="87"/>
+      <c r="L39" s="87"/>
+      <c r="M39" s="87" t="s">
         <v>4</v>
       </c>
-      <c r="N39" s="79"/>
-      <c r="O39" s="79"/>
-      <c r="P39" s="79"/>
-      <c r="Q39" s="79"/>
-      <c r="R39" s="79"/>
-      <c r="S39" s="79"/>
+      <c r="N39" s="87"/>
+      <c r="O39" s="87"/>
+      <c r="P39" s="87"/>
+      <c r="Q39" s="87"/>
+      <c r="R39" s="87"/>
+      <c r="S39" s="87"/>
       <c r="T39" s="28"/>
     </row>
     <row r="40" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -2735,50 +2735,50 @@
     </row>
     <row r="41" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="26"/>
-      <c r="M41" s="88" t="s">
+      <c r="M41" s="139" t="s">
         <v>10</v>
       </c>
-      <c r="N41" s="89"/>
-      <c r="O41" s="90"/>
-      <c r="P41" s="90"/>
-      <c r="Q41" s="90"/>
-      <c r="R41" s="90"/>
-      <c r="S41" s="91"/>
+      <c r="N41" s="140"/>
+      <c r="O41" s="141"/>
+      <c r="P41" s="141"/>
+      <c r="Q41" s="141"/>
+      <c r="R41" s="141"/>
+      <c r="S41" s="142"/>
       <c r="T41" s="63"/>
     </row>
     <row r="42" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="26"/>
       <c r="B42" s="18"/>
-      <c r="M42" s="81" t="s">
+      <c r="M42" s="130" t="s">
         <v>58</v>
       </c>
-      <c r="N42" s="82"/>
-      <c r="O42" s="142"/>
-      <c r="P42" s="142"/>
-      <c r="Q42" s="142"/>
-      <c r="R42" s="142"/>
-      <c r="S42" s="143"/>
+      <c r="N42" s="131"/>
+      <c r="O42" s="132"/>
+      <c r="P42" s="132"/>
+      <c r="Q42" s="132"/>
+      <c r="R42" s="132"/>
+      <c r="S42" s="133"/>
       <c r="T42" s="63"/>
     </row>
     <row r="43" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="26"/>
       <c r="B43" s="19"/>
-      <c r="D43" s="80"/>
-      <c r="E43" s="80"/>
-      <c r="F43" s="80"/>
-      <c r="G43" s="80"/>
-      <c r="H43" s="80"/>
-      <c r="I43" s="80"/>
-      <c r="J43" s="80"/>
-      <c r="K43" s="80"/>
-      <c r="M43" s="83" t="s">
+      <c r="D43" s="129"/>
+      <c r="E43" s="129"/>
+      <c r="F43" s="129"/>
+      <c r="G43" s="129"/>
+      <c r="H43" s="129"/>
+      <c r="I43" s="129"/>
+      <c r="J43" s="129"/>
+      <c r="K43" s="129"/>
+      <c r="M43" s="134" t="s">
         <v>60</v>
       </c>
-      <c r="N43" s="84"/>
-      <c r="O43" s="85"/>
-      <c r="P43" s="85"/>
-      <c r="Q43" s="85"/>
-      <c r="R43" s="85"/>
+      <c r="N43" s="135"/>
+      <c r="O43" s="136"/>
+      <c r="P43" s="136"/>
+      <c r="Q43" s="136"/>
+      <c r="R43" s="136"/>
       <c r="S43" s="64"/>
       <c r="T43" s="28"/>
     </row>
@@ -2787,10 +2787,10 @@
       <c r="B44" s="61" t="s">
         <v>51</v>
       </c>
-      <c r="H44" s="87"/>
-      <c r="I44" s="87"/>
-      <c r="J44" s="87"/>
-      <c r="K44" s="87"/>
+      <c r="H44" s="138"/>
+      <c r="I44" s="138"/>
+      <c r="J44" s="138"/>
+      <c r="K44" s="138"/>
       <c r="R44" s="6"/>
       <c r="S44" s="6"/>
       <c r="T44" s="28"/>
@@ -2800,68 +2800,133 @@
       <c r="B45" s="77" t="s">
         <v>61</v>
       </c>
-      <c r="I45" s="87"/>
-      <c r="J45" s="87"/>
-      <c r="K45" s="87"/>
-      <c r="L45" s="87"/>
-      <c r="M45" s="87"/>
-      <c r="N45" s="87"/>
-      <c r="O45" s="87"/>
-      <c r="P45" s="87"/>
-      <c r="Q45" s="87"/>
-      <c r="R45" s="87"/>
-      <c r="S45" s="87"/>
+      <c r="I45" s="138"/>
+      <c r="J45" s="138"/>
+      <c r="K45" s="138"/>
+      <c r="L45" s="138"/>
+      <c r="M45" s="138"/>
+      <c r="N45" s="138"/>
+      <c r="O45" s="138"/>
+      <c r="P45" s="138"/>
+      <c r="Q45" s="138"/>
+      <c r="R45" s="138"/>
+      <c r="S45" s="138"/>
       <c r="T45" s="28"/>
     </row>
     <row r="46" spans="1:20" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A46" s="36"/>
-      <c r="B46" s="86" t="s">
+      <c r="B46" s="137" t="s">
         <v>5</v>
       </c>
-      <c r="C46" s="86"/>
-      <c r="D46" s="86"/>
-      <c r="E46" s="86"/>
-      <c r="F46" s="86"/>
-      <c r="G46" s="86"/>
-      <c r="H46" s="86"/>
-      <c r="I46" s="86"/>
-      <c r="J46" s="86"/>
-      <c r="K46" s="86"/>
-      <c r="L46" s="86"/>
-      <c r="M46" s="86"/>
-      <c r="N46" s="86"/>
-      <c r="O46" s="86"/>
-      <c r="P46" s="86"/>
-      <c r="Q46" s="86"/>
-      <c r="R46" s="86"/>
-      <c r="S46" s="86"/>
+      <c r="C46" s="137"/>
+      <c r="D46" s="137"/>
+      <c r="E46" s="137"/>
+      <c r="F46" s="137"/>
+      <c r="G46" s="137"/>
+      <c r="H46" s="137"/>
+      <c r="I46" s="137"/>
+      <c r="J46" s="137"/>
+      <c r="K46" s="137"/>
+      <c r="L46" s="137"/>
+      <c r="M46" s="137"/>
+      <c r="N46" s="137"/>
+      <c r="O46" s="137"/>
+      <c r="P46" s="137"/>
+      <c r="Q46" s="137"/>
+      <c r="R46" s="137"/>
+      <c r="S46" s="137"/>
       <c r="T46" s="76"/>
     </row>
     <row r="47" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B47" s="78" t="s">
+      <c r="B47" s="128" t="s">
         <v>36</v>
       </c>
-      <c r="C47" s="78"/>
-      <c r="D47" s="78"/>
-      <c r="E47" s="78"/>
-      <c r="F47" s="78"/>
-      <c r="G47" s="78"/>
-      <c r="H47" s="78"/>
-      <c r="I47" s="78"/>
-      <c r="J47" s="78"/>
-      <c r="K47" s="78"/>
-      <c r="L47" s="78"/>
-      <c r="M47" s="78"/>
-      <c r="N47" s="78"/>
-      <c r="O47" s="78"/>
-      <c r="P47" s="78"/>
-      <c r="Q47" s="78"/>
-      <c r="R47" s="78"/>
-      <c r="S47" s="78"/>
-      <c r="T47" s="78"/>
+      <c r="C47" s="128"/>
+      <c r="D47" s="128"/>
+      <c r="E47" s="128"/>
+      <c r="F47" s="128"/>
+      <c r="G47" s="128"/>
+      <c r="H47" s="128"/>
+      <c r="I47" s="128"/>
+      <c r="J47" s="128"/>
+      <c r="K47" s="128"/>
+      <c r="L47" s="128"/>
+      <c r="M47" s="128"/>
+      <c r="N47" s="128"/>
+      <c r="O47" s="128"/>
+      <c r="P47" s="128"/>
+      <c r="Q47" s="128"/>
+      <c r="R47" s="128"/>
+      <c r="S47" s="128"/>
+      <c r="T47" s="128"/>
     </row>
   </sheetData>
   <mergeCells count="81">
+    <mergeCell ref="B47:T47"/>
+    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="I39:L39"/>
+    <mergeCell ref="M39:S39"/>
+    <mergeCell ref="D43:K43"/>
+    <mergeCell ref="M42:N42"/>
+    <mergeCell ref="O42:S42"/>
+    <mergeCell ref="M43:N43"/>
+    <mergeCell ref="O43:R43"/>
+    <mergeCell ref="B46:S46"/>
+    <mergeCell ref="I45:S45"/>
+    <mergeCell ref="H44:K44"/>
+    <mergeCell ref="M41:N41"/>
+    <mergeCell ref="O41:S41"/>
+    <mergeCell ref="B38:H38"/>
+    <mergeCell ref="I38:L38"/>
+    <mergeCell ref="M38:S38"/>
+    <mergeCell ref="J31:M31"/>
+    <mergeCell ref="J33:M33"/>
+    <mergeCell ref="J32:M32"/>
+    <mergeCell ref="J34:M34"/>
+    <mergeCell ref="Q31:S31"/>
+    <mergeCell ref="N35:P35"/>
+    <mergeCell ref="Q35:S35"/>
+    <mergeCell ref="J35:M35"/>
+    <mergeCell ref="I36:S36"/>
+    <mergeCell ref="B37:H37"/>
+    <mergeCell ref="I37:L37"/>
+    <mergeCell ref="M37:S37"/>
+    <mergeCell ref="N29:P29"/>
+    <mergeCell ref="Q29:S29"/>
+    <mergeCell ref="J29:M29"/>
+    <mergeCell ref="N31:P31"/>
+    <mergeCell ref="Q34:S34"/>
+    <mergeCell ref="N34:P34"/>
+    <mergeCell ref="Q33:S33"/>
+    <mergeCell ref="N33:P33"/>
+    <mergeCell ref="Q32:S32"/>
+    <mergeCell ref="N32:P32"/>
+    <mergeCell ref="J30:M30"/>
+    <mergeCell ref="N30:P30"/>
+    <mergeCell ref="Q30:S30"/>
+    <mergeCell ref="N28:P28"/>
+    <mergeCell ref="Q28:S28"/>
+    <mergeCell ref="Q27:S27"/>
+    <mergeCell ref="L25:M25"/>
+    <mergeCell ref="C26:I26"/>
+    <mergeCell ref="J28:M28"/>
+    <mergeCell ref="Q25:S25"/>
+    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="C27:I27"/>
+    <mergeCell ref="K15:S15"/>
+    <mergeCell ref="C25:I25"/>
+    <mergeCell ref="L26:M26"/>
+    <mergeCell ref="Q26:S26"/>
+    <mergeCell ref="Q5:S5"/>
+    <mergeCell ref="H7:N7"/>
+    <mergeCell ref="I17:S17"/>
+    <mergeCell ref="Q7:S7"/>
+    <mergeCell ref="G11:S11"/>
+    <mergeCell ref="G12:S12"/>
+    <mergeCell ref="G13:S13"/>
+    <mergeCell ref="G14:J14"/>
+    <mergeCell ref="G15:J15"/>
+    <mergeCell ref="P22:R22"/>
     <mergeCell ref="Q2:S2"/>
     <mergeCell ref="D20:S20"/>
     <mergeCell ref="L24:M24"/>
@@ -2878,71 +2943,6 @@
     <mergeCell ref="F22:I22"/>
     <mergeCell ref="H8:N8"/>
     <mergeCell ref="O5:P5"/>
-    <mergeCell ref="K15:S15"/>
-    <mergeCell ref="C25:I25"/>
-    <mergeCell ref="L26:M26"/>
-    <mergeCell ref="Q26:S26"/>
-    <mergeCell ref="Q5:S5"/>
-    <mergeCell ref="H7:N7"/>
-    <mergeCell ref="I17:S17"/>
-    <mergeCell ref="Q7:S7"/>
-    <mergeCell ref="G11:S11"/>
-    <mergeCell ref="G12:S12"/>
-    <mergeCell ref="G13:S13"/>
-    <mergeCell ref="G14:J14"/>
-    <mergeCell ref="G15:J15"/>
-    <mergeCell ref="P22:R22"/>
-    <mergeCell ref="N28:P28"/>
-    <mergeCell ref="Q28:S28"/>
-    <mergeCell ref="Q27:S27"/>
-    <mergeCell ref="L25:M25"/>
-    <mergeCell ref="C26:I26"/>
-    <mergeCell ref="J28:M28"/>
-    <mergeCell ref="Q25:S25"/>
-    <mergeCell ref="L27:M27"/>
-    <mergeCell ref="C27:I27"/>
-    <mergeCell ref="N29:P29"/>
-    <mergeCell ref="Q29:S29"/>
-    <mergeCell ref="J29:M29"/>
-    <mergeCell ref="N31:P31"/>
-    <mergeCell ref="Q34:S34"/>
-    <mergeCell ref="N34:P34"/>
-    <mergeCell ref="Q33:S33"/>
-    <mergeCell ref="N33:P33"/>
-    <mergeCell ref="Q32:S32"/>
-    <mergeCell ref="N32:P32"/>
-    <mergeCell ref="J30:M30"/>
-    <mergeCell ref="N30:P30"/>
-    <mergeCell ref="Q30:S30"/>
-    <mergeCell ref="B38:H38"/>
-    <mergeCell ref="I38:L38"/>
-    <mergeCell ref="M38:S38"/>
-    <mergeCell ref="J31:M31"/>
-    <mergeCell ref="J33:M33"/>
-    <mergeCell ref="J32:M32"/>
-    <mergeCell ref="J34:M34"/>
-    <mergeCell ref="Q31:S31"/>
-    <mergeCell ref="N35:P35"/>
-    <mergeCell ref="Q35:S35"/>
-    <mergeCell ref="J35:M35"/>
-    <mergeCell ref="I36:S36"/>
-    <mergeCell ref="B37:H37"/>
-    <mergeCell ref="I37:L37"/>
-    <mergeCell ref="M37:S37"/>
-    <mergeCell ref="B47:T47"/>
-    <mergeCell ref="B39:H39"/>
-    <mergeCell ref="I39:L39"/>
-    <mergeCell ref="M39:S39"/>
-    <mergeCell ref="D43:K43"/>
-    <mergeCell ref="M42:N42"/>
-    <mergeCell ref="O42:S42"/>
-    <mergeCell ref="M43:N43"/>
-    <mergeCell ref="O43:R43"/>
-    <mergeCell ref="B46:S46"/>
-    <mergeCell ref="I45:S45"/>
-    <mergeCell ref="H44:K44"/>
-    <mergeCell ref="M41:N41"/>
-    <mergeCell ref="O41:S41"/>
   </mergeCells>
   <pageMargins left="0.3" right="0" top="0.5" bottom="0" header="0.5" footer="0"/>
   <pageSetup paperSize="9" scale="91" orientation="portrait" r:id="rId1"/>
